--- a/policytone/speeches_meta.xlsx
+++ b/policytone/speeches_meta.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H538"/>
+  <dimension ref="A1:H541"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16501,12 +16501,12 @@
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>ECB_2026-07-17_697e49f8</t>
+          <t>ECB_2026-08-28_80f690ef</t>
         </is>
       </c>
       <c r="B403" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="C403" t="inlineStr">
@@ -16516,37 +16516,37 @@
       </c>
       <c r="D403" t="inlineStr">
         <is>
-          <t>Piero Cipollone</t>
+          <t>Isabel Schnabel</t>
         </is>
       </c>
       <c r="E403" t="inlineStr">
         <is>
-          <t>The cooperative spirit at the heart of the digital euro</t>
+          <t>Central banks on-chain</t>
         </is>
       </c>
       <c r="F403" t="inlineStr">
         <is>
-          <t>ecb://2026-07-17/The cooperative spirit at the heart of the digital</t>
+          <t>ecb://2026-08-28/Central banks on-chain</t>
         </is>
       </c>
       <c r="G403" t="n">
-        <v>20191</v>
+        <v>30923</v>
       </c>
       <c r="H403" t="inlineStr">
         <is>
-          <t>bodies\ECB_2026-07-17_697e49f8.txt</t>
+          <t>bodies\ECB_2026-08-28_80f690ef.txt</t>
         </is>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>ECB_2026-07-06_1c56e599</t>
+          <t>ECB_2026-08-26_5ad503e9</t>
         </is>
       </c>
       <c r="B404" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="C404" t="inlineStr">
@@ -16556,37 +16556,37 @@
       </c>
       <c r="D404" t="inlineStr">
         <is>
-          <t>Philip R. Lane</t>
+          <t>Piero Cipollone</t>
         </is>
       </c>
       <c r="E404" t="inlineStr">
         <is>
-          <t>AI and monetary policy</t>
+          <t>From vision to delivery: building Europe’s tokenised financial market</t>
         </is>
       </c>
       <c r="F404" t="inlineStr">
         <is>
-          <t>ecb://2026-07-06/AI and monetary policy</t>
+          <t>ecb://2026-08-26/From vision to delivery: building Europe’s tokenis</t>
         </is>
       </c>
       <c r="G404" t="n">
-        <v>15168</v>
+        <v>21799</v>
       </c>
       <c r="H404" t="inlineStr">
         <is>
-          <t>bodies\ECB_2026-07-06_1c56e599.txt</t>
+          <t>bodies\ECB_2026-08-26_5ad503e9.txt</t>
         </is>
       </c>
     </row>
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>ECB_2026-07-02_a23671b0</t>
+          <t>ECB_2026-08-19_5402ae4f</t>
         </is>
       </c>
       <c r="B405" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="C405" t="inlineStr">
@@ -16596,37 +16596,37 @@
       </c>
       <c r="D405" t="inlineStr">
         <is>
-          <t>Frank Elderson</t>
+          <t>Christine Lagarde</t>
         </is>
       </c>
       <c r="E405" t="inlineStr">
         <is>
-          <t>The green transition – benefits and barriers</t>
+          <t>Panel remarks about the European economy during a discussion on the global economic outlook at the World Economic Forum</t>
         </is>
       </c>
       <c r="F405" t="inlineStr">
         <is>
-          <t>ecb://2026-07-02/The green transition – benefits and barriers</t>
+          <t xml:space="preserve">ecb://2026-08-19/Panel remarks about the European economy during a </t>
         </is>
       </c>
       <c r="G405" t="n">
-        <v>36277</v>
+        <v>9970</v>
       </c>
       <c r="H405" t="inlineStr">
         <is>
-          <t>bodies\ECB_2026-07-02_a23671b0.txt</t>
+          <t>bodies\ECB_2026-08-19_5402ae4f.txt</t>
         </is>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>ECB_2026-06-29_995043cb</t>
+          <t>ECB_2026-07-17_697e49f8</t>
         </is>
       </c>
       <c r="B406" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="C406" t="inlineStr">
@@ -16636,37 +16636,37 @@
       </c>
       <c r="D406" t="inlineStr">
         <is>
-          <t>Christine Lagarde</t>
+          <t>Piero Cipollone</t>
         </is>
       </c>
       <c r="E406" t="inlineStr">
         <is>
-          <t>Back to basics in an uncertain environment</t>
+          <t>The cooperative spirit at the heart of the digital euro</t>
         </is>
       </c>
       <c r="F406" t="inlineStr">
         <is>
-          <t>ecb://2026-06-29/Back to basics in an uncertain environment</t>
+          <t>ecb://2026-07-17/The cooperative spirit at the heart of the digital</t>
         </is>
       </c>
       <c r="G406" t="n">
-        <v>18205</v>
+        <v>20191</v>
       </c>
       <c r="H406" t="inlineStr">
         <is>
-          <t>bodies\ECB_2026-06-29_995043cb.txt</t>
+          <t>bodies\ECB_2026-07-17_697e49f8.txt</t>
         </is>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>ECB_2026-06-23_c31a47b9</t>
+          <t>ECB_2026-07-06_1c56e599</t>
         </is>
       </c>
       <c r="B407" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="C407" t="inlineStr">
@@ -16681,32 +16681,32 @@
       </c>
       <c r="E407" t="inlineStr">
         <is>
-          <t>Introductory remarks</t>
+          <t>AI and monetary policy</t>
         </is>
       </c>
       <c r="F407" t="inlineStr">
         <is>
-          <t>ecb://2026-06-23/Introductory remarks</t>
+          <t>ecb://2026-07-06/AI and monetary policy</t>
         </is>
       </c>
       <c r="G407" t="n">
-        <v>8014</v>
+        <v>15168</v>
       </c>
       <c r="H407" t="inlineStr">
         <is>
-          <t>bodies\ECB_2026-06-23_c31a47b9.txt</t>
+          <t>bodies\ECB_2026-07-06_1c56e599.txt</t>
         </is>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t>ECB_2026-06-22_6aeaa045</t>
+          <t>ECB_2026-07-02_a23671b0</t>
         </is>
       </c>
       <c r="B408" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="C408" t="inlineStr">
@@ -16716,37 +16716,37 @@
       </c>
       <c r="D408" t="inlineStr">
         <is>
-          <t>Christine Lagarde</t>
+          <t>Frank Elderson</t>
         </is>
       </c>
       <c r="E408" t="inlineStr">
         <is>
-          <t>Hearing of the Committee on Economic and Monetary Affairs of the European Parliament</t>
+          <t>The green transition – benefits and barriers</t>
         </is>
       </c>
       <c r="F408" t="inlineStr">
         <is>
-          <t xml:space="preserve">ecb://2026-06-22/Hearing of the Committee on Economic and Monetary </t>
+          <t>ecb://2026-07-02/The green transition – benefits and barriers</t>
         </is>
       </c>
       <c r="G408" t="n">
-        <v>12686</v>
+        <v>36277</v>
       </c>
       <c r="H408" t="inlineStr">
         <is>
-          <t>bodies\ECB_2026-06-22_6aeaa045.txt</t>
+          <t>bodies\ECB_2026-07-02_a23671b0.txt</t>
         </is>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t>ECB_2026-06-19_a4708bdd</t>
+          <t>ECB_2026-06-29_995043cb</t>
         </is>
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="C409" t="inlineStr">
@@ -16756,37 +16756,37 @@
       </c>
       <c r="D409" t="inlineStr">
         <is>
-          <t>Frank Elderson</t>
+          <t>Christine Lagarde</t>
         </is>
       </c>
       <c r="E409" t="inlineStr">
         <is>
-          <t>Fireside chat</t>
+          <t>Back to basics in an uncertain environment</t>
         </is>
       </c>
       <c r="F409" t="inlineStr">
         <is>
-          <t>ecb://2026-06-19/Fireside chat</t>
+          <t>ecb://2026-06-29/Back to basics in an uncertain environment</t>
         </is>
       </c>
       <c r="G409" t="n">
-        <v>23576</v>
+        <v>18205</v>
       </c>
       <c r="H409" t="inlineStr">
         <is>
-          <t>bodies\ECB_2026-06-19_a4708bdd.txt</t>
+          <t>bodies\ECB_2026-06-29_995043cb.txt</t>
         </is>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="inlineStr">
         <is>
-          <t>ECB_2026-06-03_e367fde2</t>
+          <t>ECB_2026-06-23_c31a47b9</t>
         </is>
       </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="C410" t="inlineStr">
@@ -16796,37 +16796,37 @@
       </c>
       <c r="D410" t="inlineStr">
         <is>
-          <t>Frank Elderson</t>
+          <t>Philip R. Lane</t>
         </is>
       </c>
       <c r="E410" t="inlineStr">
         <is>
-          <t>Strengthening operational resilience for the age of AI</t>
+          <t>Introductory remarks</t>
         </is>
       </c>
       <c r="F410" t="inlineStr">
         <is>
-          <t>ecb://2026-06-03/Strengthening operational resilience for the age o</t>
+          <t>ecb://2026-06-23/Introductory remarks</t>
         </is>
       </c>
       <c r="G410" t="n">
-        <v>21203</v>
+        <v>8014</v>
       </c>
       <c r="H410" t="inlineStr">
         <is>
-          <t>bodies\ECB_2026-06-03_e367fde2.txt</t>
+          <t>bodies\ECB_2026-06-23_c31a47b9.txt</t>
         </is>
       </c>
     </row>
     <row r="411">
       <c r="A411" t="inlineStr">
         <is>
-          <t>ECB_2026-05-28_1aa28284</t>
+          <t>ECB_2026-06-22_6aeaa045</t>
         </is>
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="C411" t="inlineStr">
@@ -16836,37 +16836,37 @@
       </c>
       <c r="D411" t="inlineStr">
         <is>
-          <t>Piero Cipollone</t>
+          <t>Christine Lagarde</t>
         </is>
       </c>
       <c r="E411" t="inlineStr">
         <is>
-          <t>Money in the digital age</t>
+          <t>Hearing of the Committee on Economic and Monetary Affairs of the European Parliament</t>
         </is>
       </c>
       <c r="F411" t="inlineStr">
         <is>
-          <t>ecb://2026-05-28/Money in the digital age</t>
+          <t xml:space="preserve">ecb://2026-06-22/Hearing of the Committee on Economic and Monetary </t>
         </is>
       </c>
       <c r="G411" t="n">
-        <v>16123</v>
+        <v>12686</v>
       </c>
       <c r="H411" t="inlineStr">
         <is>
-          <t>bodies\ECB_2026-05-28_1aa28284.txt</t>
+          <t>bodies\ECB_2026-06-22_6aeaa045.txt</t>
         </is>
       </c>
     </row>
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
-          <t>ECB_2026-05-28_21d8d727</t>
+          <t>ECB_2026-06-19_a4708bdd</t>
         </is>
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="C412" t="inlineStr">
@@ -16876,37 +16876,37 @@
       </c>
       <c r="D412" t="inlineStr">
         <is>
-          <t>Christine Lagarde</t>
+          <t>Frank Elderson</t>
         </is>
       </c>
       <c r="E412" t="inlineStr">
         <is>
-          <t>When It Matters Most: Upholding Independence in Challenging Times</t>
+          <t>Fireside chat</t>
         </is>
       </c>
       <c r="F412" t="inlineStr">
         <is>
-          <t>ecb://2026-05-28/When It Matters Most: Upholding Independence in Ch</t>
+          <t>ecb://2026-06-19/Fireside chat</t>
         </is>
       </c>
       <c r="G412" t="n">
-        <v>13138</v>
+        <v>23576</v>
       </c>
       <c r="H412" t="inlineStr">
         <is>
-          <t>bodies\ECB_2026-05-28_21d8d727.txt</t>
+          <t>bodies\ECB_2026-06-19_a4708bdd.txt</t>
         </is>
       </c>
     </row>
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
-          <t>ECB_2026-05-22_a6a8ad78</t>
+          <t>ECB_2026-06-03_e367fde2</t>
         </is>
       </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="C413" t="inlineStr">
@@ -16916,37 +16916,37 @@
       </c>
       <c r="D413" t="inlineStr">
         <is>
-          <t>Philip R. Lane</t>
+          <t>Frank Elderson</t>
         </is>
       </c>
       <c r="E413" t="inlineStr">
         <is>
-          <t>Europe and the world economy</t>
+          <t>Strengthening operational resilience for the age of AI</t>
         </is>
       </c>
       <c r="F413" t="inlineStr">
         <is>
-          <t>ecb://2026-05-22/Europe and the world economy</t>
+          <t>ecb://2026-06-03/Strengthening operational resilience for the age o</t>
         </is>
       </c>
       <c r="G413" t="n">
-        <v>92948</v>
+        <v>21203</v>
       </c>
       <c r="H413" t="inlineStr">
         <is>
-          <t>bodies\ECB_2026-05-22_a6a8ad78.txt</t>
+          <t>bodies\ECB_2026-06-03_e367fde2.txt</t>
         </is>
       </c>
     </row>
     <row r="414">
       <c r="A414" t="inlineStr">
         <is>
-          <t>ECB_2026-05-13_a6bbd9bd</t>
+          <t>ECB_2026-05-28_1aa28284</t>
         </is>
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="C414" t="inlineStr">
@@ -16956,37 +16956,37 @@
       </c>
       <c r="D414" t="inlineStr">
         <is>
-          <t>Christine Lagarde</t>
+          <t>Piero Cipollone</t>
         </is>
       </c>
       <c r="E414" t="inlineStr">
         <is>
-          <t>The courage to build a Europe that endures</t>
+          <t>Money in the digital age</t>
         </is>
       </c>
       <c r="F414" t="inlineStr">
         <is>
-          <t>ecb://2026-05-13/The courage to build a Europe that endures</t>
+          <t>ecb://2026-05-28/Money in the digital age</t>
         </is>
       </c>
       <c r="G414" t="n">
-        <v>8547</v>
+        <v>16123</v>
       </c>
       <c r="H414" t="inlineStr">
         <is>
-          <t>bodies\ECB_2026-05-13_a6bbd9bd.txt</t>
+          <t>bodies\ECB_2026-05-28_1aa28284.txt</t>
         </is>
       </c>
     </row>
     <row r="415">
       <c r="A415" t="inlineStr">
         <is>
-          <t>ECB_2026-05-13_399ea1a2</t>
+          <t>ECB_2026-05-28_21d8d727</t>
         </is>
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="C415" t="inlineStr">
@@ -16996,37 +16996,37 @@
       </c>
       <c r="D415" t="inlineStr">
         <is>
-          <t>Philip R. Lane</t>
+          <t>Christine Lagarde</t>
         </is>
       </c>
       <c r="E415" t="inlineStr">
         <is>
-          <t>Analytical perspectives on energy supply shocks</t>
+          <t>When It Matters Most: Upholding Independence in Challenging Times</t>
         </is>
       </c>
       <c r="F415" t="inlineStr">
         <is>
-          <t>ecb://2026-05-13/Analytical perspectives on energy supply shocks</t>
+          <t>ecb://2026-05-28/When It Matters Most: Upholding Independence in Ch</t>
         </is>
       </c>
       <c r="G415" t="n">
-        <v>32689</v>
+        <v>13138</v>
       </c>
       <c r="H415" t="inlineStr">
         <is>
-          <t>bodies\ECB_2026-05-13_399ea1a2.txt</t>
+          <t>bodies\ECB_2026-05-28_21d8d727.txt</t>
         </is>
       </c>
     </row>
     <row r="416">
       <c r="A416" t="inlineStr">
         <is>
-          <t>ECB_2026-05-12_db14ea64</t>
+          <t>ECB_2026-05-22_a6a8ad78</t>
         </is>
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="C416" t="inlineStr">
@@ -17036,37 +17036,37 @@
       </c>
       <c r="D416" t="inlineStr">
         <is>
-          <t>Frank Elderson</t>
+          <t>Philip R. Lane</t>
         </is>
       </c>
       <c r="E416" t="inlineStr">
         <is>
-          <t>Boosting prosperity through deeper integration</t>
+          <t>Europe and the world economy</t>
         </is>
       </c>
       <c r="F416" t="inlineStr">
         <is>
-          <t>ecb://2026-05-12/Boosting prosperity through deeper integration</t>
+          <t>ecb://2026-05-22/Europe and the world economy</t>
         </is>
       </c>
       <c r="G416" t="n">
-        <v>18057</v>
+        <v>92948</v>
       </c>
       <c r="H416" t="inlineStr">
         <is>
-          <t>bodies\ECB_2026-05-12_db14ea64.txt</t>
+          <t>bodies\ECB_2026-05-22_a6a8ad78.txt</t>
         </is>
       </c>
     </row>
     <row r="417">
       <c r="A417" t="inlineStr">
         <is>
-          <t>ECB_2026-05-07_f0f97eb4</t>
+          <t>ECB_2026-05-13_a6bbd9bd</t>
         </is>
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="C417" t="inlineStr">
@@ -17076,37 +17076,37 @@
       </c>
       <c r="D417" t="inlineStr">
         <is>
-          <t>Isabel Schnabel</t>
+          <t>Christine Lagarde</t>
         </is>
       </c>
       <c r="E417" t="inlineStr">
         <is>
-          <t>The quiet erosion of central bank independence</t>
+          <t>The courage to build a Europe that endures</t>
         </is>
       </c>
       <c r="F417" t="inlineStr">
         <is>
-          <t>ecb://2026-05-07/The quiet erosion of central bank independence</t>
+          <t>ecb://2026-05-13/The courage to build a Europe that endures</t>
         </is>
       </c>
       <c r="G417" t="n">
-        <v>37620</v>
+        <v>8547</v>
       </c>
       <c r="H417" t="inlineStr">
         <is>
-          <t>bodies\ECB_2026-05-07_f0f97eb4.txt</t>
+          <t>bodies\ECB_2026-05-13_a6bbd9bd.txt</t>
         </is>
       </c>
     </row>
     <row r="418">
       <c r="A418" t="inlineStr">
         <is>
-          <t>ECB_2026-05-07_b743c434</t>
+          <t>ECB_2026-05-13_399ea1a2</t>
         </is>
       </c>
       <c r="B418" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="C418" t="inlineStr">
@@ -17116,37 +17116,37 @@
       </c>
       <c r="D418" t="inlineStr">
         <is>
-          <t>Luis de Guindos</t>
+          <t>Philip R. Lane</t>
         </is>
       </c>
       <c r="E418" t="inlineStr">
         <is>
-          <t>Deepening financial integration to support Europe’s prosperity</t>
+          <t>Analytical perspectives on energy supply shocks</t>
         </is>
       </c>
       <c r="F418" t="inlineStr">
         <is>
-          <t>ecb://2026-05-07/Deepening financial integration to support Europe’</t>
+          <t>ecb://2026-05-13/Analytical perspectives on energy supply shocks</t>
         </is>
       </c>
       <c r="G418" t="n">
-        <v>10410</v>
+        <v>32689</v>
       </c>
       <c r="H418" t="inlineStr">
         <is>
-          <t>bodies\ECB_2026-05-07_b743c434.txt</t>
+          <t>bodies\ECB_2026-05-13_399ea1a2.txt</t>
         </is>
       </c>
     </row>
     <row r="419">
       <c r="A419" t="inlineStr">
         <is>
-          <t>ECB_2026-05-06_be30907e</t>
+          <t>ECB_2026-05-12_db14ea64</t>
         </is>
       </c>
       <c r="B419" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="C419" t="inlineStr">
@@ -17156,37 +17156,37 @@
       </c>
       <c r="D419" t="inlineStr">
         <is>
-          <t>Piero Cipollone</t>
+          <t>Frank Elderson</t>
         </is>
       </c>
       <c r="E419" t="inlineStr">
         <is>
-          <t>The new energy shock: economic scenarios and policy implications</t>
+          <t>Boosting prosperity through deeper integration</t>
         </is>
       </c>
       <c r="F419" t="inlineStr">
         <is>
-          <t>ecb://2026-05-06/The new energy shock: economic scenarios and polic</t>
+          <t>ecb://2026-05-12/Boosting prosperity through deeper integration</t>
         </is>
       </c>
       <c r="G419" t="n">
-        <v>30373</v>
+        <v>18057</v>
       </c>
       <c r="H419" t="inlineStr">
         <is>
-          <t>bodies\ECB_2026-05-06_be30907e.txt</t>
+          <t>bodies\ECB_2026-05-12_db14ea64.txt</t>
         </is>
       </c>
     </row>
     <row r="420">
       <c r="A420" t="inlineStr">
         <is>
-          <t>ECB_2026-05-04_f6a25b18</t>
+          <t>ECB_2026-05-07_f0f97eb4</t>
         </is>
       </c>
       <c r="B420" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="C420" t="inlineStr">
@@ -17196,37 +17196,37 @@
       </c>
       <c r="D420" t="inlineStr">
         <is>
-          <t>Luis de Guindos</t>
+          <t>Isabel Schnabel</t>
         </is>
       </c>
       <c r="E420" t="inlineStr">
         <is>
-          <t>Presentation of the ECB Annual Report 2025 to the Committee on Economic and Monetary Affairs of the European Parliament</t>
+          <t>The quiet erosion of central bank independence</t>
         </is>
       </c>
       <c r="F420" t="inlineStr">
         <is>
-          <t xml:space="preserve">ecb://2026-05-04/Presentation of the ECB Annual Report 2025 to the </t>
+          <t>ecb://2026-05-07/The quiet erosion of central bank independence</t>
         </is>
       </c>
       <c r="G420" t="n">
-        <v>7015</v>
+        <v>37620</v>
       </c>
       <c r="H420" t="inlineStr">
         <is>
-          <t>bodies\ECB_2026-05-04_f6a25b18.txt</t>
+          <t>bodies\ECB_2026-05-07_f0f97eb4.txt</t>
         </is>
       </c>
     </row>
     <row r="421">
       <c r="A421" t="inlineStr">
         <is>
-          <t>ECB_2026-04-22_babfe6eb</t>
+          <t>ECB_2026-05-07_b743c434</t>
         </is>
       </c>
       <c r="B421" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="C421" t="inlineStr">
@@ -17236,37 +17236,37 @@
       </c>
       <c r="D421" t="inlineStr">
         <is>
-          <t>Philip R. Lane</t>
+          <t>Luis de Guindos</t>
         </is>
       </c>
       <c r="E421" t="inlineStr">
         <is>
-          <t>Expanding the supply of euro safe assets</t>
+          <t>Deepening financial integration to support Europe’s prosperity</t>
         </is>
       </c>
       <c r="F421" t="inlineStr">
         <is>
-          <t>ecb://2026-04-22/Expanding the supply of euro safe assets</t>
+          <t>ecb://2026-05-07/Deepening financial integration to support Europe’</t>
         </is>
       </c>
       <c r="G421" t="n">
-        <v>14948</v>
+        <v>10410</v>
       </c>
       <c r="H421" t="inlineStr">
         <is>
-          <t>bodies\ECB_2026-04-22_babfe6eb.txt</t>
+          <t>bodies\ECB_2026-05-07_b743c434.txt</t>
         </is>
       </c>
     </row>
     <row r="422">
       <c r="A422" t="inlineStr">
         <is>
-          <t>ECB_2026-04-20_07a3de6d</t>
+          <t>ECB_2026-05-06_be30907e</t>
         </is>
       </c>
       <c r="B422" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="C422" t="inlineStr">
@@ -17276,37 +17276,37 @@
       </c>
       <c r="D422" t="inlineStr">
         <is>
-          <t>Christine Lagarde</t>
+          <t>Piero Cipollone</t>
         </is>
       </c>
       <c r="E422" t="inlineStr">
         <is>
-          <t>The energy shock: where we stand and what we need to know</t>
+          <t>The new energy shock: economic scenarios and policy implications</t>
         </is>
       </c>
       <c r="F422" t="inlineStr">
         <is>
-          <t xml:space="preserve">ecb://2026-04-20/The energy shock: where we stand and what we need </t>
+          <t>ecb://2026-05-06/The new energy shock: economic scenarios and polic</t>
         </is>
       </c>
       <c r="G422" t="n">
-        <v>11035</v>
+        <v>30373</v>
       </c>
       <c r="H422" t="inlineStr">
         <is>
-          <t>bodies\ECB_2026-04-20_07a3de6d.txt</t>
+          <t>bodies\ECB_2026-05-06_be30907e.txt</t>
         </is>
       </c>
     </row>
     <row r="423">
       <c r="A423" t="inlineStr">
         <is>
-          <t>ECB_2026-04-17_a0d69641</t>
+          <t>ECB_2026-05-04_f6a25b18</t>
         </is>
       </c>
       <c r="B423" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="C423" t="inlineStr">
@@ -17316,37 +17316,37 @@
       </c>
       <c r="D423" t="inlineStr">
         <is>
-          <t>Christine Lagarde</t>
+          <t>Luis de Guindos</t>
         </is>
       </c>
       <c r="E423" t="inlineStr">
         <is>
-          <t>IMFC Statement</t>
+          <t>Presentation of the ECB Annual Report 2025 to the Committee on Economic and Monetary Affairs of the European Parliament</t>
         </is>
       </c>
       <c r="F423" t="inlineStr">
         <is>
-          <t>ecb://2026-04-17/IMFC Statement</t>
+          <t xml:space="preserve">ecb://2026-05-04/Presentation of the ECB Annual Report 2025 to the </t>
         </is>
       </c>
       <c r="G423" t="n">
-        <v>14068</v>
+        <v>7015</v>
       </c>
       <c r="H423" t="inlineStr">
         <is>
-          <t>bodies\ECB_2026-04-17_a0d69641.txt</t>
+          <t>bodies\ECB_2026-05-04_f6a25b18.txt</t>
         </is>
       </c>
     </row>
     <row r="424">
       <c r="A424" t="inlineStr">
         <is>
-          <t>ECB_2026-04-15_131a5028</t>
+          <t>ECB_2026-04-22_babfe6eb</t>
         </is>
       </c>
       <c r="B424" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="C424" t="inlineStr">
@@ -17356,37 +17356,37 @@
       </c>
       <c r="D424" t="inlineStr">
         <is>
-          <t>Piero Cipollone</t>
+          <t>Philip R. Lane</t>
         </is>
       </c>
       <c r="E424" t="inlineStr">
         <is>
-          <t>Sparking the transformation of finance: tokenisation and the role of central banks</t>
+          <t>Expanding the supply of euro safe assets</t>
         </is>
       </c>
       <c r="F424" t="inlineStr">
         <is>
-          <t>ecb://2026-04-15/Sparking the transformation of finance: tokenisati</t>
+          <t>ecb://2026-04-22/Expanding the supply of euro safe assets</t>
         </is>
       </c>
       <c r="G424" t="n">
-        <v>20039</v>
+        <v>14948</v>
       </c>
       <c r="H424" t="inlineStr">
         <is>
-          <t>bodies\ECB_2026-04-15_131a5028.txt</t>
+          <t>bodies\ECB_2026-04-22_babfe6eb.txt</t>
         </is>
       </c>
     </row>
     <row r="425">
       <c r="A425" t="inlineStr">
         <is>
-          <t>ECB_2026-03-26_28ef9b81</t>
+          <t>ECB_2026-04-20_07a3de6d</t>
         </is>
       </c>
       <c r="B425" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="C425" t="inlineStr">
@@ -17396,37 +17396,37 @@
       </c>
       <c r="D425" t="inlineStr">
         <is>
-          <t>Luis de Guindos</t>
+          <t>Christine Lagarde</t>
         </is>
       </c>
       <c r="E425" t="inlineStr">
         <is>
-          <t>Navigating turbulence: challenges for Europe and the path ahead</t>
+          <t>The energy shock: where we stand and what we need to know</t>
         </is>
       </c>
       <c r="F425" t="inlineStr">
         <is>
-          <t>ecb://2026-03-26/Navigating turbulence: challenges for Europe and t</t>
+          <t xml:space="preserve">ecb://2026-04-20/The energy shock: where we stand and what we need </t>
         </is>
       </c>
       <c r="G425" t="n">
-        <v>13175</v>
+        <v>11035</v>
       </c>
       <c r="H425" t="inlineStr">
         <is>
-          <t>bodies\ECB_2026-03-26_28ef9b81.txt</t>
+          <t>bodies\ECB_2026-04-20_07a3de6d.txt</t>
         </is>
       </c>
     </row>
     <row r="426">
       <c r="A426" t="inlineStr">
         <is>
-          <t>ECB_2026-03-25_944ba9f2</t>
+          <t>ECB_2026-04-17_a0d69641</t>
         </is>
       </c>
       <c r="B426" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="C426" t="inlineStr">
@@ -17441,32 +17441,32 @@
       </c>
       <c r="E426" t="inlineStr">
         <is>
-          <t>Navigating energy shocks: risks and policy responses</t>
+          <t>IMFC Statement</t>
         </is>
       </c>
       <c r="F426" t="inlineStr">
         <is>
-          <t>ecb://2026-03-25/Navigating energy shocks: risks and policy respons</t>
+          <t>ecb://2026-04-17/IMFC Statement</t>
         </is>
       </c>
       <c r="G426" t="n">
-        <v>19064</v>
+        <v>14068</v>
       </c>
       <c r="H426" t="inlineStr">
         <is>
-          <t>bodies\ECB_2026-03-25_944ba9f2.txt</t>
+          <t>bodies\ECB_2026-04-17_a0d69641.txt</t>
         </is>
       </c>
     </row>
     <row r="427">
       <c r="A427" t="inlineStr">
         <is>
-          <t>ECB_2026-03-24_bb8e2f74</t>
+          <t>ECB_2026-04-15_131a5028</t>
         </is>
       </c>
       <c r="B427" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="C427" t="inlineStr">
@@ -17481,32 +17481,32 @@
       </c>
       <c r="E427" t="inlineStr">
         <is>
-          <t>The digital euro: preparing for a potential launch</t>
+          <t>Sparking the transformation of finance: tokenisation and the role of central banks</t>
         </is>
       </c>
       <c r="F427" t="inlineStr">
         <is>
-          <t>ecb://2026-03-24/The digital euro: preparing for a potential launch</t>
+          <t>ecb://2026-04-15/Sparking the transformation of finance: tokenisati</t>
         </is>
       </c>
       <c r="G427" t="n">
-        <v>21607</v>
+        <v>20039</v>
       </c>
       <c r="H427" t="inlineStr">
         <is>
-          <t>bodies\ECB_2026-03-24_bb8e2f74.txt</t>
+          <t>bodies\ECB_2026-04-15_131a5028.txt</t>
         </is>
       </c>
     </row>
     <row r="428">
       <c r="A428" t="inlineStr">
         <is>
-          <t>ECB_2026-03-23_579e7301</t>
+          <t>ECB_2026-03-26_28ef9b81</t>
         </is>
       </c>
       <c r="B428" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="C428" t="inlineStr">
@@ -17516,37 +17516,37 @@
       </c>
       <c r="D428" t="inlineStr">
         <is>
-          <t>Philip R. Lane</t>
+          <t>Luis de Guindos</t>
         </is>
       </c>
       <c r="E428" t="inlineStr">
         <is>
-          <t>AI and the euro area economy</t>
+          <t>Navigating turbulence: challenges for Europe and the path ahead</t>
         </is>
       </c>
       <c r="F428" t="inlineStr">
         <is>
-          <t>ecb://2026-03-23/AI and the euro area economy</t>
+          <t>ecb://2026-03-26/Navigating turbulence: challenges for Europe and t</t>
         </is>
       </c>
       <c r="G428" t="n">
-        <v>95352</v>
+        <v>13175</v>
       </c>
       <c r="H428" t="inlineStr">
         <is>
-          <t>bodies\ECB_2026-03-23_579e7301.txt</t>
+          <t>bodies\ECB_2026-03-26_28ef9b81.txt</t>
         </is>
       </c>
     </row>
     <row r="429">
       <c r="A429" t="inlineStr">
         <is>
-          <t>ECB_2026-03-23_b70c0c3d</t>
+          <t>ECB_2026-03-25_944ba9f2</t>
         </is>
       </c>
       <c r="B429" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="C429" t="inlineStr">
@@ -17556,37 +17556,37 @@
       </c>
       <c r="D429" t="inlineStr">
         <is>
-          <t>Piero Cipollone</t>
+          <t>Christine Lagarde</t>
         </is>
       </c>
       <c r="E429" t="inlineStr">
         <is>
-          <t>Building the rails for Europe’s tokenised financial markets</t>
+          <t>Navigating energy shocks: risks and policy responses</t>
         </is>
       </c>
       <c r="F429" t="inlineStr">
         <is>
-          <t>ecb://2026-03-23/Building the rails for Europe’s tokenised financia</t>
+          <t>ecb://2026-03-25/Navigating energy shocks: risks and policy respons</t>
         </is>
       </c>
       <c r="G429" t="n">
-        <v>15403</v>
+        <v>19064</v>
       </c>
       <c r="H429" t="inlineStr">
         <is>
-          <t>bodies\ECB_2026-03-23_b70c0c3d.txt</t>
+          <t>bodies\ECB_2026-03-25_944ba9f2.txt</t>
         </is>
       </c>
     </row>
     <row r="430">
       <c r="A430" t="inlineStr">
         <is>
-          <t>ECB_2026-03-09_1d6fb010</t>
+          <t>ECB_2026-03-24_bb8e2f74</t>
         </is>
       </c>
       <c r="B430" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="C430" t="inlineStr">
@@ -17596,37 +17596,37 @@
       </c>
       <c r="D430" t="inlineStr">
         <is>
-          <t>Frank Elderson</t>
+          <t>Piero Cipollone</t>
         </is>
       </c>
       <c r="E430" t="inlineStr">
         <is>
-          <t>Nature in decline, economy on the line: the importance of international cooperation for managing nature-related risks</t>
+          <t>The digital euro: preparing for a potential launch</t>
         </is>
       </c>
       <c r="F430" t="inlineStr">
         <is>
-          <t>ecb://2026-03-09/Nature in decline, economy on the line: the import</t>
+          <t>ecb://2026-03-24/The digital euro: preparing for a potential launch</t>
         </is>
       </c>
       <c r="G430" t="n">
-        <v>16080</v>
+        <v>21607</v>
       </c>
       <c r="H430" t="inlineStr">
         <is>
-          <t>bodies\ECB_2026-03-09_1d6fb010.txt</t>
+          <t>bodies\ECB_2026-03-24_bb8e2f74.txt</t>
         </is>
       </c>
     </row>
     <row r="431">
       <c r="A431" t="inlineStr">
         <is>
-          <t>ECB_2026-03-06_085ba49a</t>
+          <t>ECB_2026-03-23_579e7301</t>
         </is>
       </c>
       <c r="B431" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="C431" t="inlineStr">
@@ -17636,37 +17636,37 @@
       </c>
       <c r="D431" t="inlineStr">
         <is>
-          <t>Isabel Schnabel</t>
+          <t>Philip R. Lane</t>
         </is>
       </c>
       <c r="E431" t="inlineStr">
         <is>
-          <t>Navigating inflation and employment in an era of supply shocks and AI</t>
+          <t>AI and the euro area economy</t>
         </is>
       </c>
       <c r="F431" t="inlineStr">
         <is>
-          <t>ecb://2026-03-06/Navigating inflation and employment in an era of s</t>
+          <t>ecb://2026-03-23/AI and the euro area economy</t>
         </is>
       </c>
       <c r="G431" t="n">
-        <v>31230</v>
+        <v>95352</v>
       </c>
       <c r="H431" t="inlineStr">
         <is>
-          <t>bodies\ECB_2026-03-06_085ba49a.txt</t>
+          <t>bodies\ECB_2026-03-23_579e7301.txt</t>
         </is>
       </c>
     </row>
     <row r="432">
       <c r="A432" t="inlineStr">
         <is>
-          <t>ECB_2026-03-05_71408458</t>
+          <t>ECB_2026-03-23_b70c0c3d</t>
         </is>
       </c>
       <c r="B432" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="C432" t="inlineStr">
@@ -17676,37 +17676,37 @@
       </c>
       <c r="D432" t="inlineStr">
         <is>
-          <t>Christine Lagarde</t>
+          <t>Piero Cipollone</t>
         </is>
       </c>
       <c r="E432" t="inlineStr">
         <is>
-          <t>Technology, fragmentation and the new uncertainty</t>
+          <t>Building the rails for Europe’s tokenised financial markets</t>
         </is>
       </c>
       <c r="F432" t="inlineStr">
         <is>
-          <t>ecb://2026-03-05/Technology, fragmentation and the new uncertainty</t>
+          <t>ecb://2026-03-23/Building the rails for Europe’s tokenised financia</t>
         </is>
       </c>
       <c r="G432" t="n">
-        <v>22140</v>
+        <v>15403</v>
       </c>
       <c r="H432" t="inlineStr">
         <is>
-          <t>bodies\ECB_2026-03-05_71408458.txt</t>
+          <t>bodies\ECB_2026-03-23_b70c0c3d.txt</t>
         </is>
       </c>
     </row>
     <row r="433">
       <c r="A433" t="inlineStr">
         <is>
-          <t>ECB_2026-02-26_31ed3b69</t>
+          <t>ECB_2026-03-09_1d6fb010</t>
         </is>
       </c>
       <c r="B433" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="C433" t="inlineStr">
@@ -17716,37 +17716,37 @@
       </c>
       <c r="D433" t="inlineStr">
         <is>
-          <t>Christine Lagarde</t>
+          <t>Frank Elderson</t>
         </is>
       </c>
       <c r="E433" t="inlineStr">
         <is>
-          <t>Hearing of the Committee on Economic and Monetary Affairs of the European Parliament</t>
+          <t>Nature in decline, economy on the line: the importance of international cooperation for managing nature-related risks</t>
         </is>
       </c>
       <c r="F433" t="inlineStr">
         <is>
-          <t xml:space="preserve">ecb://2026-02-26/Hearing of the Committee on Economic and Monetary </t>
+          <t>ecb://2026-03-09/Nature in decline, economy on the line: the import</t>
         </is>
       </c>
       <c r="G433" t="n">
-        <v>13454</v>
+        <v>16080</v>
       </c>
       <c r="H433" t="inlineStr">
         <is>
-          <t>bodies\ECB_2026-02-26_31ed3b69.txt</t>
+          <t>bodies\ECB_2026-03-09_1d6fb010.txt</t>
         </is>
       </c>
     </row>
     <row r="434">
       <c r="A434" t="inlineStr">
         <is>
-          <t>ECB_2026-02-23_8611c067</t>
+          <t>ECB_2026-03-06_085ba49a</t>
         </is>
       </c>
       <c r="B434" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="C434" t="inlineStr">
@@ -17756,37 +17756,37 @@
       </c>
       <c r="D434" t="inlineStr">
         <is>
-          <t>Christine Lagarde</t>
+          <t>Isabel Schnabel</t>
         </is>
       </c>
       <c r="E434" t="inlineStr">
         <is>
-          <t>Turning size into scale: Europe’s new growth model</t>
+          <t>Navigating inflation and employment in an era of supply shocks and AI</t>
         </is>
       </c>
       <c r="F434" t="inlineStr">
         <is>
-          <t>ecb://2026-02-23/Turning size into scale: Europe’s new growth model</t>
+          <t>ecb://2026-03-06/Navigating inflation and employment in an era of s</t>
         </is>
       </c>
       <c r="G434" t="n">
-        <v>21732</v>
+        <v>31230</v>
       </c>
       <c r="H434" t="inlineStr">
         <is>
-          <t>bodies\ECB_2026-02-23_8611c067.txt</t>
+          <t>bodies\ECB_2026-03-06_085ba49a.txt</t>
         </is>
       </c>
     </row>
     <row r="435">
       <c r="A435" t="inlineStr">
         <is>
-          <t>ECB_2026-02-20_e3a80a1c</t>
+          <t>ECB_2026-03-05_71408458</t>
         </is>
       </c>
       <c r="B435" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="C435" t="inlineStr">
@@ -17801,32 +17801,32 @@
       </c>
       <c r="E435" t="inlineStr">
         <is>
-          <t>The order that took centuries to build</t>
+          <t>Technology, fragmentation and the new uncertainty</t>
         </is>
       </c>
       <c r="F435" t="inlineStr">
         <is>
-          <t>ecb://2026-02-20/The order that took centuries to build</t>
+          <t>ecb://2026-03-05/Technology, fragmentation and the new uncertainty</t>
         </is>
       </c>
       <c r="G435" t="n">
-        <v>17065</v>
+        <v>22140</v>
       </c>
       <c r="H435" t="inlineStr">
         <is>
-          <t>bodies\ECB_2026-02-20_e3a80a1c.txt</t>
+          <t>bodies\ECB_2026-03-05_71408458.txt</t>
         </is>
       </c>
     </row>
     <row r="436">
       <c r="A436" t="inlineStr">
         <is>
-          <t>ECB_2026-02-14_28b206ae</t>
+          <t>ECB_2026-02-26_31ed3b69</t>
         </is>
       </c>
       <c r="B436" t="inlineStr">
         <is>
-          <t>2026-02-14</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="C436" t="inlineStr">
@@ -17841,32 +17841,32 @@
       </c>
       <c r="E436" t="inlineStr">
         <is>
-          <t>Preparing for geoeconomic fragmentation</t>
+          <t>Hearing of the Committee on Economic and Monetary Affairs of the European Parliament</t>
         </is>
       </c>
       <c r="F436" t="inlineStr">
         <is>
-          <t>ecb://2026-02-14/Preparing for geoeconomic fragmentation</t>
+          <t xml:space="preserve">ecb://2026-02-26/Hearing of the Committee on Economic and Monetary </t>
         </is>
       </c>
       <c r="G436" t="n">
-        <v>5191</v>
+        <v>13454</v>
       </c>
       <c r="H436" t="inlineStr">
         <is>
-          <t>bodies\ECB_2026-02-14_28b206ae.txt</t>
+          <t>bodies\ECB_2026-02-26_31ed3b69.txt</t>
         </is>
       </c>
     </row>
     <row r="437">
       <c r="A437" t="inlineStr">
         <is>
-          <t>ECB_2026-02-12_74faf1fb</t>
+          <t>ECB_2026-02-23_8611c067</t>
         </is>
       </c>
       <c r="B437" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="C437" t="inlineStr">
@@ -17876,37 +17876,37 @@
       </c>
       <c r="D437" t="inlineStr">
         <is>
-          <t>Philip R. Lane</t>
+          <t>Christine Lagarde</t>
         </is>
       </c>
       <c r="E437" t="inlineStr">
         <is>
-          <t>Bulgaria and the euro</t>
+          <t>Turning size into scale: Europe’s new growth model</t>
         </is>
       </c>
       <c r="F437" t="inlineStr">
         <is>
-          <t>ecb://2026-02-12/Bulgaria and the euro</t>
+          <t>ecb://2026-02-23/Turning size into scale: Europe’s new growth model</t>
         </is>
       </c>
       <c r="G437" t="n">
-        <v>12336</v>
+        <v>21732</v>
       </c>
       <c r="H437" t="inlineStr">
         <is>
-          <t>bodies\ECB_2026-02-12_74faf1fb.txt</t>
+          <t>bodies\ECB_2026-02-23_8611c067.txt</t>
         </is>
       </c>
     </row>
     <row r="438">
       <c r="A438" t="inlineStr">
         <is>
-          <t>ECB_2026-02-12_ad1e1e68</t>
+          <t>ECB_2026-02-20_e3a80a1c</t>
         </is>
       </c>
       <c r="B438" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="C438" t="inlineStr">
@@ -17916,37 +17916,37 @@
       </c>
       <c r="D438" t="inlineStr">
         <is>
-          <t>Piero Cipollone</t>
+          <t>Christine Lagarde</t>
         </is>
       </c>
       <c r="E438" t="inlineStr">
         <is>
-          <t>Europe and monetary sovereignty</t>
+          <t>The order that took centuries to build</t>
         </is>
       </c>
       <c r="F438" t="inlineStr">
         <is>
-          <t>ecb://2026-02-12/Europe and monetary sovereignty</t>
+          <t>ecb://2026-02-20/The order that took centuries to build</t>
         </is>
       </c>
       <c r="G438" t="n">
-        <v>43798</v>
+        <v>17065</v>
       </c>
       <c r="H438" t="inlineStr">
         <is>
-          <t>bodies\ECB_2026-02-12_ad1e1e68.txt</t>
+          <t>bodies\ECB_2026-02-20_e3a80a1c.txt</t>
         </is>
       </c>
     </row>
     <row r="439">
       <c r="A439" t="inlineStr">
         <is>
-          <t>ECB_2026-02-11_b883344b</t>
+          <t>ECB_2026-02-14_28b206ae</t>
         </is>
       </c>
       <c r="B439" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-02-14</t>
         </is>
       </c>
       <c r="C439" t="inlineStr">
@@ -17956,37 +17956,37 @@
       </c>
       <c r="D439" t="inlineStr">
         <is>
-          <t>Isabel Schnabel</t>
+          <t>Christine Lagarde</t>
         </is>
       </c>
       <c r="E439" t="inlineStr">
         <is>
-          <t>Made in Europe</t>
+          <t>Preparing for geoeconomic fragmentation</t>
         </is>
       </c>
       <c r="F439" t="inlineStr">
         <is>
-          <t>ecb://2026-02-11/Made in Europe</t>
+          <t>ecb://2026-02-14/Preparing for geoeconomic fragmentation</t>
         </is>
       </c>
       <c r="G439" t="n">
-        <v>29347</v>
+        <v>5191</v>
       </c>
       <c r="H439" t="inlineStr">
         <is>
-          <t>bodies\ECB_2026-02-11_b883344b.txt</t>
+          <t>bodies\ECB_2026-02-14_28b206ae.txt</t>
         </is>
       </c>
     </row>
     <row r="440">
       <c r="A440" t="inlineStr">
         <is>
-          <t>ECB_2026-02-09_5b6a4e8e</t>
+          <t>ECB_2026-02-12_74faf1fb</t>
         </is>
       </c>
       <c r="B440" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-02-12</t>
         </is>
       </c>
       <c r="C440" t="inlineStr">
@@ -17996,37 +17996,37 @@
       </c>
       <c r="D440" t="inlineStr">
         <is>
-          <t>Christine Lagarde</t>
+          <t>Philip R. Lane</t>
         </is>
       </c>
       <c r="E440" t="inlineStr">
         <is>
-          <t>European Parliament plenary debate on the ECB Annual Report</t>
+          <t>Bulgaria and the euro</t>
         </is>
       </c>
       <c r="F440" t="inlineStr">
         <is>
-          <t>ecb://2026-02-09/European Parliament plenary debate on the ECB Annu</t>
+          <t>ecb://2026-02-12/Bulgaria and the euro</t>
         </is>
       </c>
       <c r="G440" t="n">
-        <v>8969</v>
+        <v>12336</v>
       </c>
       <c r="H440" t="inlineStr">
         <is>
-          <t>bodies\ECB_2026-02-09_5b6a4e8e.txt</t>
+          <t>bodies\ECB_2026-02-12_74faf1fb.txt</t>
         </is>
       </c>
     </row>
     <row r="441">
       <c r="A441" t="inlineStr">
         <is>
-          <t>ECB_2026-01-28_47458e55</t>
+          <t>ECB_2026-02-12_ad1e1e68</t>
         </is>
       </c>
       <c r="B441" t="inlineStr">
         <is>
-          <t>2026-01-28</t>
+          <t>2026-02-12</t>
         </is>
       </c>
       <c r="C441" t="inlineStr">
@@ -18036,37 +18036,37 @@
       </c>
       <c r="D441" t="inlineStr">
         <is>
-          <t>Frank Elderson</t>
+          <t>Piero Cipollone</t>
         </is>
       </c>
       <c r="E441" t="inlineStr">
         <is>
-          <t>Hearing of the Committee on Economic and Monetary Affairs of the European Parliament</t>
+          <t>Europe and monetary sovereignty</t>
         </is>
       </c>
       <c r="F441" t="inlineStr">
         <is>
-          <t xml:space="preserve">ecb://2026-01-28/Hearing of the Committee on Economic and Monetary </t>
+          <t>ecb://2026-02-12/Europe and monetary sovereignty</t>
         </is>
       </c>
       <c r="G441" t="n">
-        <v>9462</v>
+        <v>43798</v>
       </c>
       <c r="H441" t="inlineStr">
         <is>
-          <t>bodies\ECB_2026-01-28_47458e55.txt</t>
+          <t>bodies\ECB_2026-02-12_ad1e1e68.txt</t>
         </is>
       </c>
     </row>
     <row r="442">
       <c r="A442" t="inlineStr">
         <is>
-          <t>ECB_2026-01-14_5409561c</t>
+          <t>ECB_2026-02-11_b883344b</t>
         </is>
       </c>
       <c r="B442" t="inlineStr">
         <is>
-          <t>2026-01-14</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="C442" t="inlineStr">
@@ -18076,37 +18076,37 @@
       </c>
       <c r="D442" t="inlineStr">
         <is>
-          <t>Luis de Guindos</t>
+          <t>Isabel Schnabel</t>
         </is>
       </c>
       <c r="E442" t="inlineStr">
         <is>
-          <t>Monetary policy and financial stability in the euro area</t>
+          <t>Made in Europe</t>
         </is>
       </c>
       <c r="F442" t="inlineStr">
         <is>
-          <t>ecb://2026-01-14/Monetary policy and financial stability in the eur</t>
+          <t>ecb://2026-02-11/Made in Europe</t>
         </is>
       </c>
       <c r="G442" t="n">
-        <v>10531</v>
+        <v>29347</v>
       </c>
       <c r="H442" t="inlineStr">
         <is>
-          <t>bodies\ECB_2026-01-14_5409561c.txt</t>
+          <t>bodies\ECB_2026-02-11_b883344b.txt</t>
         </is>
       </c>
     </row>
     <row r="443">
       <c r="A443" t="inlineStr">
         <is>
-          <t>ECB_2026-01-09_25216dd9</t>
+          <t>ECB_2026-02-09_5b6a4e8e</t>
         </is>
       </c>
       <c r="B443" t="inlineStr">
         <is>
-          <t>2026-01-09</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="C443" t="inlineStr">
@@ -18116,157 +18116,157 @@
       </c>
       <c r="D443" t="inlineStr">
         <is>
-          <t>Philip R. Lane</t>
+          <t>Christine Lagarde</t>
         </is>
       </c>
       <c r="E443" t="inlineStr">
         <is>
-          <t>The euro in a changing world</t>
+          <t>European Parliament plenary debate on the ECB Annual Report</t>
         </is>
       </c>
       <c r="F443" t="inlineStr">
         <is>
-          <t>ecb://2026-01-09/The euro in a changing world</t>
+          <t>ecb://2026-02-09/European Parliament plenary debate on the ECB Annu</t>
         </is>
       </c>
       <c r="G443" t="n">
-        <v>28599</v>
+        <v>8969</v>
       </c>
       <c r="H443" t="inlineStr">
         <is>
-          <t>bodies\ECB_2026-01-09_25216dd9.txt</t>
+          <t>bodies\ECB_2026-02-09_5b6a4e8e.txt</t>
         </is>
       </c>
     </row>
     <row r="444">
       <c r="A444" t="inlineStr">
         <is>
-          <t>BOE_2026-06-02_17aaf48e</t>
+          <t>ECB_2026-01-28_47458e55</t>
         </is>
       </c>
       <c r="B444" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-01-28</t>
         </is>
       </c>
       <c r="C444" t="inlineStr">
         <is>
-          <t>BOE</t>
+          <t>ECB</t>
         </is>
       </c>
       <c r="D444" t="inlineStr">
         <is>
-          <t>Dave Ramsden</t>
+          <t>Frank Elderson</t>
         </is>
       </c>
       <c r="E444" t="inlineStr">
         <is>
-          <t>Outlier or laggard: divergence and convergence in the UK’s recent inflation performance - speech by Dave Ramsden</t>
+          <t>Hearing of the Committee on Economic and Monetary Affairs of the European Parliament</t>
         </is>
       </c>
       <c r="F444" t="inlineStr">
         <is>
-          <t>https://www.bankofengland.co.uk/speech/2024/april/dave-ramsden-pannellist-at-peterson-institute-for-international-economics-conference</t>
+          <t xml:space="preserve">ecb://2026-01-28/Hearing of the Committee on Economic and Monetary </t>
         </is>
       </c>
       <c r="G444" t="n">
-        <v>21468</v>
+        <v>9462</v>
       </c>
       <c r="H444" t="inlineStr">
         <is>
-          <t>bodies\BOE_2026-06-02_17aaf48e.txt</t>
+          <t>bodies\ECB_2026-01-28_47458e55.txt</t>
         </is>
       </c>
     </row>
     <row r="445">
       <c r="A445" t="inlineStr">
         <is>
-          <t>BOE_2026-06-02_9751d418</t>
+          <t>ECB_2026-01-14_5409561c</t>
         </is>
       </c>
       <c r="B445" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-01-14</t>
         </is>
       </c>
       <c r="C445" t="inlineStr">
         <is>
-          <t>BOE</t>
+          <t>ECB</t>
         </is>
       </c>
       <c r="D445" t="inlineStr">
         <is>
-          <t>Huw Pill</t>
+          <t>Luis de Guindos</t>
         </is>
       </c>
       <c r="E445" t="inlineStr">
         <is>
-          <t>Strategy and stance – remarks by Huw Pill</t>
+          <t>Monetary policy and financial stability in the euro area</t>
         </is>
       </c>
       <c r="F445" t="inlineStr">
         <is>
-          <t>https://www.bankofengland.co.uk/speech/2024/april/huw-pill-speech-at-univeristy-of-chicago-booth-business-school</t>
+          <t>ecb://2026-01-14/Monetary policy and financial stability in the eur</t>
         </is>
       </c>
       <c r="G445" t="n">
-        <v>21560</v>
+        <v>10531</v>
       </c>
       <c r="H445" t="inlineStr">
         <is>
-          <t>bodies\BOE_2026-06-02_9751d418.txt</t>
+          <t>bodies\ECB_2026-01-14_5409561c.txt</t>
         </is>
       </c>
     </row>
     <row r="446">
       <c r="A446" t="inlineStr">
         <is>
-          <t>BOE_2026-05-29_2ee92bc8</t>
+          <t>ECB_2026-01-09_25216dd9</t>
         </is>
       </c>
       <c r="B446" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-01-09</t>
         </is>
       </c>
       <c r="C446" t="inlineStr">
         <is>
-          <t>BOE</t>
+          <t>ECB</t>
         </is>
       </c>
       <c r="D446" t="inlineStr">
         <is>
-          <t>Andrew Bailey</t>
+          <t>Philip R. Lane</t>
         </is>
       </c>
       <c r="E446" t="inlineStr">
         <is>
-          <t>Reflecting on recent times – speech by Andrew Bailey</t>
+          <t>The euro in a changing world</t>
         </is>
       </c>
       <c r="F446" t="inlineStr">
         <is>
-          <t>https://www.bankofengland.co.uk/speech/2024/august/andrew-bailey-speech-federal-reserve-bank-of-kansas-annual-jackson-hole-economic-policy-symposium</t>
+          <t>ecb://2026-01-09/The euro in a changing world</t>
         </is>
       </c>
       <c r="G446" t="n">
-        <v>24535</v>
+        <v>28599</v>
       </c>
       <c r="H446" t="inlineStr">
         <is>
-          <t>bodies\BOE_2026-05-29_2ee92bc8.txt</t>
+          <t>bodies\ECB_2026-01-09_25216dd9.txt</t>
         </is>
       </c>
     </row>
     <row r="447">
       <c r="A447" t="inlineStr">
         <is>
-          <t>BOE_2026-06-16_809a81f8</t>
+          <t>BOE_2026-06-02_17aaf48e</t>
         </is>
       </c>
       <c r="B447" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="C447" t="inlineStr">
@@ -18281,27 +18281,27 @@
       </c>
       <c r="E447" t="inlineStr">
         <is>
-          <t>Getting the balance right: ensuring the Bank’s balance sheet can support financial stability − speech by Dave Ramsden</t>
+          <t>Outlier or laggard: divergence and convergence in the UK’s recent inflation performance - speech by Dave Ramsden</t>
         </is>
       </c>
       <c r="F447" t="inlineStr">
         <is>
-          <t>https://www.bankofengland.co.uk/speech/2024/december/dave-ramsden-speech-at-omfif-on-financial-stability-and-the-boe-toolkit</t>
+          <t>https://www.bankofengland.co.uk/speech/2024/april/dave-ramsden-pannellist-at-peterson-institute-for-international-economics-conference</t>
         </is>
       </c>
       <c r="G447" t="n">
-        <v>32460</v>
+        <v>21468</v>
       </c>
       <c r="H447" t="inlineStr">
         <is>
-          <t>bodies\BOE_2026-06-16_809a81f8.txt</t>
+          <t>bodies\BOE_2026-06-02_17aaf48e.txt</t>
         </is>
       </c>
     </row>
     <row r="448">
       <c r="A448" t="inlineStr">
         <is>
-          <t>BOE_2026-06-02_391c35b0</t>
+          <t>BOE_2026-06-02_9751d418</t>
         </is>
       </c>
       <c r="B448" t="inlineStr">
@@ -18316,37 +18316,37 @@
       </c>
       <c r="D448" t="inlineStr">
         <is>
-          <t>Andrew Bailey</t>
+          <t>Huw Pill</t>
         </is>
       </c>
       <c r="E448" t="inlineStr">
         <is>
-          <t>Loughborough lecture: Banking today - speech by Andrew Bailey</t>
+          <t>Strategy and stance – remarks by Huw Pill</t>
         </is>
       </c>
       <c r="F448" t="inlineStr">
         <is>
-          <t>https://www.bankofengland.co.uk/speech/2024/february/andrew-bailey-lecture-at-loughborough-university</t>
+          <t>https://www.bankofengland.co.uk/speech/2024/april/huw-pill-speech-at-univeristy-of-chicago-booth-business-school</t>
         </is>
       </c>
       <c r="G448" t="n">
-        <v>30543</v>
+        <v>21560</v>
       </c>
       <c r="H448" t="inlineStr">
         <is>
-          <t>bodies\BOE_2026-06-02_391c35b0.txt</t>
+          <t>bodies\BOE_2026-06-02_9751d418.txt</t>
         </is>
       </c>
     </row>
     <row r="449">
       <c r="A449" t="inlineStr">
         <is>
-          <t>BOE_2026-06-02_5304c9f6</t>
+          <t>BOE_2026-05-29_2ee92bc8</t>
         </is>
       </c>
       <c r="B449" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="C449" t="inlineStr">
@@ -18356,37 +18356,37 @@
       </c>
       <c r="D449" t="inlineStr">
         <is>
-          <t>Catherine L. Mann</t>
+          <t>Andrew Bailey</t>
         </is>
       </c>
       <c r="E449" t="inlineStr">
         <is>
-          <t>Mind the gap(s): Inflation data and prospects - speech by Catherine L. Mann</t>
+          <t>Reflecting on recent times – speech by Andrew Bailey</t>
         </is>
       </c>
       <c r="F449" t="inlineStr">
         <is>
-          <t>https://www.bankofengland.co.uk/speech/2024/february/catherine-l-mann-speech-at-the-official-monetary-and-financial-institution</t>
+          <t>https://www.bankofengland.co.uk/speech/2024/august/andrew-bailey-speech-federal-reserve-bank-of-kansas-annual-jackson-hole-economic-policy-symposium</t>
         </is>
       </c>
       <c r="G449" t="n">
-        <v>22710</v>
+        <v>24535</v>
       </c>
       <c r="H449" t="inlineStr">
         <is>
-          <t>bodies\BOE_2026-06-02_5304c9f6.txt</t>
+          <t>bodies\BOE_2026-05-29_2ee92bc8.txt</t>
         </is>
       </c>
     </row>
     <row r="450">
       <c r="A450" t="inlineStr">
         <is>
-          <t>BOE_2026-05-29_c9fc86eb</t>
+          <t>BOE_2026-06-16_809a81f8</t>
         </is>
       </c>
       <c r="B450" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="C450" t="inlineStr">
@@ -18401,27 +18401,27 @@
       </c>
       <c r="E450" t="inlineStr">
         <is>
-          <t>Bond trading, innovation and evolution: a Bank of England Perspective − speech by Dave Ramsden</t>
+          <t>Getting the balance right: ensuring the Bank’s balance sheet can support financial stability − speech by Dave Ramsden</t>
         </is>
       </c>
       <c r="F450" t="inlineStr">
         <is>
-          <t>https://www.bankofengland.co.uk/speech/2024/february/david-ramsden-keynote-address-at-association-for-financial-markets-forum</t>
+          <t>https://www.bankofengland.co.uk/speech/2024/december/dave-ramsden-speech-at-omfif-on-financial-stability-and-the-boe-toolkit</t>
         </is>
       </c>
       <c r="G450" t="n">
-        <v>28449</v>
+        <v>32460</v>
       </c>
       <c r="H450" t="inlineStr">
         <is>
-          <t>bodies\BOE_2026-05-29_c9fc86eb.txt</t>
+          <t>bodies\BOE_2026-06-16_809a81f8.txt</t>
         </is>
       </c>
     </row>
     <row r="451">
       <c r="A451" t="inlineStr">
         <is>
-          <t>BOE_2026-06-02_c6e72b81</t>
+          <t>BOE_2026-06-02_391c35b0</t>
         </is>
       </c>
       <c r="B451" t="inlineStr">
@@ -18436,32 +18436,32 @@
       </c>
       <c r="D451" t="inlineStr">
         <is>
-          <t>Megan Greene</t>
+          <t>Andrew Bailey</t>
         </is>
       </c>
       <c r="E451" t="inlineStr">
         <is>
-          <t>Worlds apart? UK inflation and monetary policy in an international context - speech by Megan Greene</t>
+          <t>Loughborough lecture: Banking today - speech by Andrew Bailey</t>
         </is>
       </c>
       <c r="F451" t="inlineStr">
         <is>
-          <t>https://www.bankofengland.co.uk/speech/2024/february/megan-greene-fireside-chat-with-brian-coulton-chief-economist-fitch-ratings</t>
+          <t>https://www.bankofengland.co.uk/speech/2024/february/andrew-bailey-lecture-at-loughborough-university</t>
         </is>
       </c>
       <c r="G451" t="n">
-        <v>23917</v>
+        <v>30543</v>
       </c>
       <c r="H451" t="inlineStr">
         <is>
-          <t>bodies\BOE_2026-06-02_c6e72b81.txt</t>
+          <t>bodies\BOE_2026-06-02_391c35b0.txt</t>
         </is>
       </c>
     </row>
     <row r="452">
       <c r="A452" t="inlineStr">
         <is>
-          <t>BOE_2026-06-02_afba3264</t>
+          <t>BOE_2026-06-02_5304c9f6</t>
         </is>
       </c>
       <c r="B452" t="inlineStr">
@@ -18476,37 +18476,37 @@
       </c>
       <c r="D452" t="inlineStr">
         <is>
-          <t>Sarah Breeden</t>
+          <t>Catherine L. Mann</t>
         </is>
       </c>
       <c r="E452" t="inlineStr">
         <is>
-          <t>Engineering revisited - speech by Sarah Breeden</t>
+          <t>Mind the gap(s): Inflation data and prospects - speech by Catherine L. Mann</t>
         </is>
       </c>
       <c r="F452" t="inlineStr">
         <is>
-          <t>https://www.bankofengland.co.uk/speech/2024/february/sarah-breeden-keynote-speech-uk-women-in-economics-annual-networking</t>
+          <t>https://www.bankofengland.co.uk/speech/2024/february/catherine-l-mann-speech-at-the-official-monetary-and-financial-institution</t>
         </is>
       </c>
       <c r="G452" t="n">
-        <v>12543</v>
+        <v>22710</v>
       </c>
       <c r="H452" t="inlineStr">
         <is>
-          <t>bodies\BOE_2026-06-02_afba3264.txt</t>
+          <t>bodies\BOE_2026-06-02_5304c9f6.txt</t>
         </is>
       </c>
     </row>
     <row r="453">
       <c r="A453" t="inlineStr">
         <is>
-          <t>BOE_2026-06-02_6d6cf00f</t>
+          <t>BOE_2026-05-29_c9fc86eb</t>
         </is>
       </c>
       <c r="B453" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="C453" t="inlineStr">
@@ -18516,37 +18516,37 @@
       </c>
       <c r="D453" t="inlineStr">
         <is>
-          <t>Swati Dhingra</t>
+          <t>Dave Ramsden</t>
         </is>
       </c>
       <c r="E453" t="inlineStr">
         <is>
-          <t>Money’s too tight (to mention)  – speech by Swati Dhingra</t>
+          <t>Bond trading, innovation and evolution: a Bank of England Perspective − speech by Dave Ramsden</t>
         </is>
       </c>
       <c r="F453" t="inlineStr">
         <is>
-          <t>https://www.bankofengland.co.uk/speech/2024/february/swati-dhingra-market-news-international-connect-event</t>
+          <t>https://www.bankofengland.co.uk/speech/2024/february/david-ramsden-keynote-address-at-association-for-financial-markets-forum</t>
         </is>
       </c>
       <c r="G453" t="n">
-        <v>32000</v>
+        <v>28449</v>
       </c>
       <c r="H453" t="inlineStr">
         <is>
-          <t>bodies\BOE_2026-06-02_6d6cf00f.txt</t>
+          <t>bodies\BOE_2026-05-29_c9fc86eb.txt</t>
         </is>
       </c>
     </row>
     <row r="454">
       <c r="A454" t="inlineStr">
         <is>
-          <t>BOE_2026-05-29_802cfc91</t>
+          <t>BOE_2026-06-02_c6e72b81</t>
         </is>
       </c>
       <c r="B454" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="C454" t="inlineStr">
@@ -18556,32 +18556,32 @@
       </c>
       <c r="D454" t="inlineStr">
         <is>
-          <t>Huw Pill</t>
+          <t>Megan Greene</t>
         </is>
       </c>
       <c r="E454" t="inlineStr">
         <is>
-          <t>Transformation and conjuncture − remarks by Huw Pill</t>
+          <t>Worlds apart? UK inflation and monetary policy in an international context - speech by Megan Greene</t>
         </is>
       </c>
       <c r="F454" t="inlineStr">
         <is>
-          <t>https://www.bankofengland.co.uk/speech/2024/july/huw-pill-speech-at-asia-house</t>
+          <t>https://www.bankofengland.co.uk/speech/2024/february/megan-greene-fireside-chat-with-brian-coulton-chief-economist-fitch-ratings</t>
         </is>
       </c>
       <c r="G454" t="n">
-        <v>18857</v>
+        <v>23917</v>
       </c>
       <c r="H454" t="inlineStr">
         <is>
-          <t>bodies\BOE_2026-05-29_802cfc91.txt</t>
+          <t>bodies\BOE_2026-06-02_c6e72b81.txt</t>
         </is>
       </c>
     </row>
     <row r="455">
       <c r="A455" t="inlineStr">
         <is>
-          <t>BOE_2026-06-02_776fcb03</t>
+          <t>BOE_2026-06-02_afba3264</t>
         </is>
       </c>
       <c r="B455" t="inlineStr">
@@ -18596,32 +18596,32 @@
       </c>
       <c r="D455" t="inlineStr">
         <is>
-          <t>Jonathan Haskel</t>
+          <t>Sarah Breeden</t>
         </is>
       </c>
       <c r="E455" t="inlineStr">
         <is>
-          <t>UK inflation: What's done and what's to come - speech by Jonathan Haskel</t>
+          <t>Engineering revisited - speech by Sarah Breeden</t>
         </is>
       </c>
       <c r="F455" t="inlineStr">
         <is>
-          <t>https://www.bankofengland.co.uk/speech/2024/july/speech-by-jonathan-haskel-at-escoe-kings-college-london</t>
+          <t>https://www.bankofengland.co.uk/speech/2024/february/sarah-breeden-keynote-speech-uk-women-in-economics-annual-networking</t>
         </is>
       </c>
       <c r="G455" t="n">
-        <v>503</v>
+        <v>12543</v>
       </c>
       <c r="H455" t="inlineStr">
         <is>
-          <t>bodies\BOE_2026-06-02_776fcb03.txt</t>
+          <t>bodies\BOE_2026-06-02_afba3264.txt</t>
         </is>
       </c>
     </row>
     <row r="456">
       <c r="A456" t="inlineStr">
         <is>
-          <t>BOE_2026-06-02_70ccfe9b</t>
+          <t>BOE_2026-06-02_6d6cf00f</t>
         </is>
       </c>
       <c r="B456" t="inlineStr">
@@ -18636,32 +18636,32 @@
       </c>
       <c r="D456" t="inlineStr">
         <is>
-          <t>Huw Pill</t>
+          <t>Swati Dhingra</t>
         </is>
       </c>
       <c r="E456" t="inlineStr">
         <is>
-          <t>Monetary Policy Strategy − remarks by Huw Pill</t>
+          <t>Money’s too tight (to mention)  – speech by Swati Dhingra</t>
         </is>
       </c>
       <c r="F456" t="inlineStr">
         <is>
-          <t>https://www.bankofengland.co.uk/speech/2024/march/huw-pill-speech-at-the-cardiff-university-business-school</t>
+          <t>https://www.bankofengland.co.uk/speech/2024/february/swati-dhingra-market-news-international-connect-event</t>
         </is>
       </c>
       <c r="G456" t="n">
-        <v>31440</v>
+        <v>32000</v>
       </c>
       <c r="H456" t="inlineStr">
         <is>
-          <t>bodies\BOE_2026-06-02_70ccfe9b.txt</t>
+          <t>bodies\BOE_2026-06-02_6d6cf00f.txt</t>
         </is>
       </c>
     </row>
     <row r="457">
       <c r="A457" t="inlineStr">
         <is>
-          <t>BOE_2026-05-29_eb6dae70</t>
+          <t>BOE_2026-05-29_802cfc91</t>
         </is>
       </c>
       <c r="B457" t="inlineStr">
@@ -18676,32 +18676,32 @@
       </c>
       <c r="D457" t="inlineStr">
         <is>
-          <t>Andrew Bailey</t>
+          <t>Huw Pill</t>
         </is>
       </c>
       <c r="E457" t="inlineStr">
         <is>
-          <t>The importance of central bank reserves - lecture by Andrew Bailey</t>
+          <t>Transformation and conjuncture − remarks by Huw Pill</t>
         </is>
       </c>
       <c r="F457" t="inlineStr">
         <is>
-          <t>https://www.bankofengland.co.uk/speech/2024/may/andrew-bailey-lecture-london-school-of-economics-charles-goodhart</t>
+          <t>https://www.bankofengland.co.uk/speech/2024/july/huw-pill-speech-at-asia-house</t>
         </is>
       </c>
       <c r="G457" t="n">
-        <v>45855</v>
+        <v>18857</v>
       </c>
       <c r="H457" t="inlineStr">
         <is>
-          <t>bodies\BOE_2026-05-29_eb6dae70.txt</t>
+          <t>bodies\BOE_2026-05-29_802cfc91.txt</t>
         </is>
       </c>
     </row>
     <row r="458">
       <c r="A458" t="inlineStr">
         <is>
-          <t>BOE_2026-06-02_21dc52f2</t>
+          <t>BOE_2026-06-02_776fcb03</t>
         </is>
       </c>
       <c r="B458" t="inlineStr">
@@ -18716,32 +18716,32 @@
       </c>
       <c r="D458" t="inlineStr">
         <is>
-          <t>Ben Broadbent</t>
+          <t>Jonathan Haskel</t>
         </is>
       </c>
       <c r="E458" t="inlineStr">
         <is>
-          <t>From NICE… to not so nice - speech by Ben Broadbent</t>
+          <t>UK inflation: What's done and what's to come - speech by Jonathan Haskel</t>
         </is>
       </c>
       <c r="F458" t="inlineStr">
         <is>
-          <t>https://www.bankofengland.co.uk/speech/2024/may/ben-broadbent-ccbs-new-evidence-on-the-monetary-transmission-mechanism-workshop</t>
+          <t>https://www.bankofengland.co.uk/speech/2024/july/speech-by-jonathan-haskel-at-escoe-kings-college-london</t>
         </is>
       </c>
       <c r="G458" t="n">
-        <v>27025</v>
+        <v>503</v>
       </c>
       <c r="H458" t="inlineStr">
         <is>
-          <t>bodies\BOE_2026-06-02_21dc52f2.txt</t>
+          <t>bodies\BOE_2026-06-02_776fcb03.txt</t>
         </is>
       </c>
     </row>
     <row r="459">
       <c r="A459" t="inlineStr">
         <is>
-          <t>BOE_2026-06-02_f1887286</t>
+          <t>BOE_2026-06-02_70ccfe9b</t>
         </is>
       </c>
       <c r="B459" t="inlineStr">
@@ -18756,37 +18756,37 @@
       </c>
       <c r="D459" t="inlineStr">
         <is>
-          <t>Catherine L. Mann</t>
+          <t>Huw Pill</t>
         </is>
       </c>
       <c r="E459" t="inlineStr">
         <is>
-          <t>Cost of capital and UK business investment: Measurement challenges and research opportunities - slides by Catherine L. Mann</t>
+          <t>Monetary Policy Strategy − remarks by Huw Pill</t>
         </is>
       </c>
       <c r="F459" t="inlineStr">
         <is>
-          <t>https://www.bankofengland.co.uk/speech/2024/may/catherine-l-mann-cost-of-capital-and-uk-business-investment-slides</t>
+          <t>https://www.bankofengland.co.uk/speech/2024/march/huw-pill-speech-at-the-cardiff-university-business-school</t>
         </is>
       </c>
       <c r="G459" t="n">
-        <v>11116</v>
+        <v>31440</v>
       </c>
       <c r="H459" t="inlineStr">
         <is>
-          <t>bodies\BOE_2026-06-02_f1887286.txt</t>
+          <t>bodies\BOE_2026-06-02_70ccfe9b.txt</t>
         </is>
       </c>
     </row>
     <row r="460">
       <c r="A460" t="inlineStr">
         <is>
-          <t>BOE_2026-06-02_27225b75</t>
+          <t>BOE_2026-05-29_eb6dae70</t>
         </is>
       </c>
       <c r="B460" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="C460" t="inlineStr">
@@ -18796,37 +18796,37 @@
       </c>
       <c r="D460" t="inlineStr">
         <is>
-          <t>Megan Greene</t>
+          <t>Andrew Bailey</t>
         </is>
       </c>
       <c r="E460" t="inlineStr">
         <is>
-          <t>Two puzzles: recent UK labour market dynamics − speech by Megan Greene</t>
+          <t>The importance of central bank reserves - lecture by Andrew Bailey</t>
         </is>
       </c>
       <c r="F460" t="inlineStr">
         <is>
-          <t>https://www.bankofengland.co.uk/speech/2024/may/megan-greene-speech-at-make-uk-the-current-state-of-britains-labour-market</t>
+          <t>https://www.bankofengland.co.uk/speech/2024/may/andrew-bailey-lecture-london-school-of-economics-charles-goodhart</t>
         </is>
       </c>
       <c r="G460" t="n">
-        <v>23980</v>
+        <v>45855</v>
       </c>
       <c r="H460" t="inlineStr">
         <is>
-          <t>bodies\BOE_2026-06-02_27225b75.txt</t>
+          <t>bodies\BOE_2026-05-29_eb6dae70.txt</t>
         </is>
       </c>
     </row>
     <row r="461">
       <c r="A461" t="inlineStr">
         <is>
-          <t>BOE_2026-05-29_f7f849d1</t>
+          <t>BOE_2026-06-02_21dc52f2</t>
         </is>
       </c>
       <c r="B461" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="C461" t="inlineStr">
@@ -18836,37 +18836,37 @@
       </c>
       <c r="D461" t="inlineStr">
         <is>
-          <t>Andrew Bailey</t>
+          <t>Ben Broadbent</t>
         </is>
       </c>
       <c r="E461" t="inlineStr">
         <is>
-          <t>Growth − speech by Andrew Bailey</t>
+          <t>From NICE… to not so nice - speech by Ben Broadbent</t>
         </is>
       </c>
       <c r="F461" t="inlineStr">
         <is>
-          <t>https://www.bankofengland.co.uk/speech/2024/november/andrew-bailey-speech-at-the-annual-financial-and-professional-services-dinner</t>
+          <t>https://www.bankofengland.co.uk/speech/2024/may/ben-broadbent-ccbs-new-evidence-on-the-monetary-transmission-mechanism-workshop</t>
         </is>
       </c>
       <c r="G461" t="n">
-        <v>12830</v>
+        <v>27025</v>
       </c>
       <c r="H461" t="inlineStr">
         <is>
-          <t>bodies\BOE_2026-05-29_f7f849d1.txt</t>
+          <t>bodies\BOE_2026-06-02_21dc52f2.txt</t>
         </is>
       </c>
     </row>
     <row r="462">
       <c r="A462" t="inlineStr">
         <is>
-          <t>BOE_2026-05-29_b260dc59</t>
+          <t>BOE_2026-06-02_f1887286</t>
         </is>
       </c>
       <c r="B462" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="C462" t="inlineStr">
@@ -18881,27 +18881,27 @@
       </c>
       <c r="E462" t="inlineStr">
         <is>
-          <t>The Great Moderation 20 years on – and beyond – speech by Catherine L. Mann</t>
+          <t>Cost of capital and UK business investment: Measurement challenges and research opportunities - slides by Catherine L. Mann</t>
         </is>
       </c>
       <c r="F462" t="inlineStr">
         <is>
-          <t>https://www.bankofengland.co.uk/speech/2024/november/catherine-l-mann-society-of-professional-economists-annual-conference</t>
+          <t>https://www.bankofengland.co.uk/speech/2024/may/catherine-l-mann-cost-of-capital-and-uk-business-investment-slides</t>
         </is>
       </c>
       <c r="G462" t="n">
-        <v>74271</v>
+        <v>11116</v>
       </c>
       <c r="H462" t="inlineStr">
         <is>
-          <t>bodies\BOE_2026-05-29_b260dc59.txt</t>
+          <t>bodies\BOE_2026-06-02_f1887286.txt</t>
         </is>
       </c>
     </row>
     <row r="463">
       <c r="A463" t="inlineStr">
         <is>
-          <t>BOE_2026-06-02_25ff0a17</t>
+          <t>BOE_2026-06-02_27225b75</t>
         </is>
       </c>
       <c r="B463" t="inlineStr">
@@ -18916,32 +18916,32 @@
       </c>
       <c r="D463" t="inlineStr">
         <is>
-          <t>Clare Lombardelli</t>
+          <t>Megan Greene</t>
         </is>
       </c>
       <c r="E463" t="inlineStr">
         <is>
-          <t>Managing the present, shaping the future - speech by Clare Lombardelli</t>
+          <t>Two puzzles: recent UK labour market dynamics − speech by Megan Greene</t>
         </is>
       </c>
       <c r="F463" t="inlineStr">
         <is>
-          <t>https://www.bankofengland.co.uk/speech/2024/november/clare-lombardelli-speech-at-the-3rd-boe-watchers-conference</t>
+          <t>https://www.bankofengland.co.uk/speech/2024/may/megan-greene-speech-at-make-uk-the-current-state-of-britains-labour-market</t>
         </is>
       </c>
       <c r="G463" t="n">
-        <v>35932</v>
+        <v>23980</v>
       </c>
       <c r="H463" t="inlineStr">
         <is>
-          <t>bodies\BOE_2026-06-02_25ff0a17.txt</t>
+          <t>bodies\BOE_2026-06-02_27225b75.txt</t>
         </is>
       </c>
     </row>
     <row r="464">
       <c r="A464" t="inlineStr">
         <is>
-          <t>BOE_2026-05-29_a926ec34</t>
+          <t>BOE_2026-05-29_f7f849d1</t>
         </is>
       </c>
       <c r="B464" t="inlineStr">
@@ -18956,32 +18956,32 @@
       </c>
       <c r="D464" t="inlineStr">
         <is>
-          <t>Dave Ramsden</t>
+          <t>Andrew Bailey</t>
         </is>
       </c>
       <c r="E464" t="inlineStr">
         <is>
-          <t>Back to the Future 2: Keeping inflation close to the 2% target − speech by Dave Ramsden</t>
+          <t>Growth − speech by Andrew Bailey</t>
         </is>
       </c>
       <c r="F464" t="inlineStr">
         <is>
-          <t>https://www.bankofengland.co.uk/speech/2024/november/dave-ramsden-speech-on-monetary-policy-at-the-university-of-leeds</t>
+          <t>https://www.bankofengland.co.uk/speech/2024/november/andrew-bailey-speech-at-the-annual-financial-and-professional-services-dinner</t>
         </is>
       </c>
       <c r="G464" t="n">
-        <v>24835</v>
+        <v>12830</v>
       </c>
       <c r="H464" t="inlineStr">
         <is>
-          <t>bodies\BOE_2026-05-29_a926ec34.txt</t>
+          <t>bodies\BOE_2026-05-29_f7f849d1.txt</t>
         </is>
       </c>
     </row>
     <row r="465">
       <c r="A465" t="inlineStr">
         <is>
-          <t>BOE_2026-05-29_099ae30d</t>
+          <t>BOE_2026-05-29_b260dc59</t>
         </is>
       </c>
       <c r="B465" t="inlineStr">
@@ -18996,37 +18996,37 @@
       </c>
       <c r="D465" t="inlineStr">
         <is>
-          <t>Swati Dhingra</t>
+          <t>Catherine L. Mann</t>
         </is>
       </c>
       <c r="E465" t="inlineStr">
         <is>
-          <t>Inflation dynamics - slides by Swati Dhingra</t>
+          <t>The Great Moderation 20 years on – and beyond – speech by Catherine L. Mann</t>
         </is>
       </c>
       <c r="F465" t="inlineStr">
         <is>
-          <t>https://www.bankofengland.co.uk/speech/2024/november/swati-dhingra-panellist-at-third-boe-watchers-conference-inflation-dynamics</t>
+          <t>https://www.bankofengland.co.uk/speech/2024/november/catherine-l-mann-society-of-professional-economists-annual-conference</t>
         </is>
       </c>
       <c r="G465" t="n">
-        <v>2221</v>
+        <v>74271</v>
       </c>
       <c r="H465" t="inlineStr">
         <is>
-          <t>bodies\BOE_2026-05-29_099ae30d.txt</t>
+          <t>bodies\BOE_2026-05-29_b260dc59.txt</t>
         </is>
       </c>
     </row>
     <row r="466">
       <c r="A466" t="inlineStr">
         <is>
-          <t>BOE_2026-05-29_8eeb3fa8</t>
+          <t>BOE_2026-06-02_25ff0a17</t>
         </is>
       </c>
       <c r="B466" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="C466" t="inlineStr">
@@ -19036,32 +19036,32 @@
       </c>
       <c r="D466" t="inlineStr">
         <is>
-          <t>Andrew Bailey</t>
+          <t>Clare Lombardelli</t>
         </is>
       </c>
       <c r="E466" t="inlineStr">
         <is>
-          <t>Today’s challenges in Financial Stability: the new and the not so new - speech by Andrew Bailey</t>
+          <t>Managing the present, shaping the future - speech by Clare Lombardelli</t>
         </is>
       </c>
       <c r="F466" t="inlineStr">
         <is>
-          <t>https://www.bankofengland.co.uk/speech/2024/october/andrew-bailey-keynote-address-at-the-bloomberg-global-regulatory-forum</t>
+          <t>https://www.bankofengland.co.uk/speech/2024/november/clare-lombardelli-speech-at-the-3rd-boe-watchers-conference</t>
         </is>
       </c>
       <c r="G466" t="n">
-        <v>17151</v>
+        <v>35932</v>
       </c>
       <c r="H466" t="inlineStr">
         <is>
-          <t>bodies\BOE_2026-05-29_8eeb3fa8.txt</t>
+          <t>bodies\BOE_2026-06-02_25ff0a17.txt</t>
         </is>
       </c>
     </row>
     <row r="467">
       <c r="A467" t="inlineStr">
         <is>
-          <t>BOE_2026-05-29_19b189b4</t>
+          <t>BOE_2026-05-29_a926ec34</t>
         </is>
       </c>
       <c r="B467" t="inlineStr">
@@ -19074,30 +19074,34 @@
           <t>BOE</t>
         </is>
       </c>
-      <c r="D467" t="inlineStr"/>
+      <c r="D467" t="inlineStr">
+        <is>
+          <t>Dave Ramsden</t>
+        </is>
+      </c>
       <c r="E467" t="inlineStr">
         <is>
-          <t>Michael D. Gill Memorial Society Lecture − Andrew Bailey</t>
+          <t>Back to the Future 2: Keeping inflation close to the 2% target − speech by Dave Ramsden</t>
         </is>
       </c>
       <c r="F467" t="inlineStr">
         <is>
-          <t>https://www.bankofengland.co.uk/speech/2024/october/andrew-bailey-mike-gill-memorial-lecture</t>
+          <t>https://www.bankofengland.co.uk/speech/2024/november/dave-ramsden-speech-on-monetary-policy-at-the-university-of-leeds</t>
         </is>
       </c>
       <c r="G467" t="n">
-        <v>13222</v>
+        <v>24835</v>
       </c>
       <c r="H467" t="inlineStr">
         <is>
-          <t>bodies\BOE_2026-05-29_19b189b4.txt</t>
+          <t>bodies\BOE_2026-05-29_a926ec34.txt</t>
         </is>
       </c>
     </row>
     <row r="468">
       <c r="A468" t="inlineStr">
         <is>
-          <t>BOE_2026-05-29_af698994</t>
+          <t>BOE_2026-05-29_099ae30d</t>
         </is>
       </c>
       <c r="B468" t="inlineStr">
@@ -19112,37 +19116,37 @@
       </c>
       <c r="D468" t="inlineStr">
         <is>
-          <t>Huw Pill</t>
+          <t>Swati Dhingra</t>
         </is>
       </c>
       <c r="E468" t="inlineStr">
         <is>
-          <t>Cross-checking − speech by Huw Pill</t>
+          <t>Inflation dynamics - slides by Swati Dhingra</t>
         </is>
       </c>
       <c r="F468" t="inlineStr">
         <is>
-          <t>https://www.bankofengland.co.uk/speech/2024/october/huw-pill-speech-at-the-institute-chartered-accounts-annual-conference</t>
+          <t>https://www.bankofengland.co.uk/speech/2024/november/swati-dhingra-panellist-at-third-boe-watchers-conference-inflation-dynamics</t>
         </is>
       </c>
       <c r="G468" t="n">
-        <v>31049</v>
+        <v>2221</v>
       </c>
       <c r="H468" t="inlineStr">
         <is>
-          <t>bodies\BOE_2026-05-29_af698994.txt</t>
+          <t>bodies\BOE_2026-05-29_099ae30d.txt</t>
         </is>
       </c>
     </row>
     <row r="469">
       <c r="A469" t="inlineStr">
         <is>
-          <t>BOE_2026-05-21_b01380a3</t>
+          <t>BOE_2026-05-29_8eeb3fa8</t>
         </is>
       </c>
       <c r="B469" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="C469" t="inlineStr">
@@ -19152,37 +19156,37 @@
       </c>
       <c r="D469" t="inlineStr">
         <is>
-          <t>Sarah Breeden</t>
+          <t>Andrew Bailey</t>
         </is>
       </c>
       <c r="E469" t="inlineStr">
         <is>
-          <t>Engaging with the machine: AI and financial stability − speech by Sarah Breeden</t>
+          <t>Today’s challenges in Financial Stability: the new and the not so new - speech by Andrew Bailey</t>
         </is>
       </c>
       <c r="F469" t="inlineStr">
         <is>
-          <t>https://www.bankofengland.co.uk/speech/2024/october/sarah-breeden-keynote-speech-at-the-hong-kong-monetary-authority</t>
+          <t>https://www.bankofengland.co.uk/speech/2024/october/andrew-bailey-keynote-address-at-the-bloomberg-global-regulatory-forum</t>
         </is>
       </c>
       <c r="G469" t="n">
-        <v>25976</v>
+        <v>17151</v>
       </c>
       <c r="H469" t="inlineStr">
         <is>
-          <t>bodies\BOE_2026-05-21_b01380a3.txt</t>
+          <t>bodies\BOE_2026-05-29_8eeb3fa8.txt</t>
         </is>
       </c>
     </row>
     <row r="470">
       <c r="A470" t="inlineStr">
         <is>
-          <t>BOE_2026-06-02_8b889139</t>
+          <t>BOE_2026-05-29_19b189b4</t>
         </is>
       </c>
       <c r="B470" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="C470" t="inlineStr">
@@ -19190,39 +19194,35 @@
           <t>BOE</t>
         </is>
       </c>
-      <c r="D470" t="inlineStr">
-        <is>
-          <t>Swati Dhingra</t>
-        </is>
-      </c>
+      <c r="D470" t="inlineStr"/>
       <c r="E470" t="inlineStr">
         <is>
-          <t>Monetary Policy: Lessons from the pandemic - slides by Swati Dhingra</t>
+          <t>Michael D. Gill Memorial Society Lecture − Andrew Bailey</t>
         </is>
       </c>
       <c r="F470" t="inlineStr">
         <is>
-          <t>https://www.bankofengland.co.uk/speech/2024/october/swati-dhingra-panellist-at-the-reserve-bank-of-india-conference</t>
+          <t>https://www.bankofengland.co.uk/speech/2024/october/andrew-bailey-mike-gill-memorial-lecture</t>
         </is>
       </c>
       <c r="G470" t="n">
-        <v>3490</v>
+        <v>13222</v>
       </c>
       <c r="H470" t="inlineStr">
         <is>
-          <t>bodies\BOE_2026-06-02_8b889139.txt</t>
+          <t>bodies\BOE_2026-05-29_19b189b4.txt</t>
         </is>
       </c>
     </row>
     <row r="471">
       <c r="A471" t="inlineStr">
         <is>
-          <t>BOE_2026-06-02_d99dbee5</t>
+          <t>BOE_2026-05-29_af698994</t>
         </is>
       </c>
       <c r="B471" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="C471" t="inlineStr">
@@ -19232,37 +19232,37 @@
       </c>
       <c r="D471" t="inlineStr">
         <is>
-          <t>Catherine L. Mann</t>
+          <t>Huw Pill</t>
         </is>
       </c>
       <c r="E471" t="inlineStr">
         <is>
-          <t>Policy spillovers when external shocks persist and domestic activity diverges - speech by Catherine L. Mann</t>
+          <t>Cross-checking − speech by Huw Pill</t>
         </is>
       </c>
       <c r="F471" t="inlineStr">
         <is>
-          <t>https://www.bankofengland.co.uk/speech/2024/september/catherine-l-mann-keynote-speech-at-the-central-bank-research-association</t>
+          <t>https://www.bankofengland.co.uk/speech/2024/october/huw-pill-speech-at-the-institute-chartered-accounts-annual-conference</t>
         </is>
       </c>
       <c r="G471" t="n">
-        <v>39410</v>
+        <v>31049</v>
       </c>
       <c r="H471" t="inlineStr">
         <is>
-          <t>bodies\BOE_2026-06-02_d99dbee5.txt</t>
+          <t>bodies\BOE_2026-05-29_af698994.txt</t>
         </is>
       </c>
     </row>
     <row r="472">
       <c r="A472" t="inlineStr">
         <is>
-          <t>BOE_2026-05-29_c3aaf9ec</t>
+          <t>BOE_2026-05-21_b01380a3</t>
         </is>
       </c>
       <c r="B472" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="C472" t="inlineStr">
@@ -19272,32 +19272,32 @@
       </c>
       <c r="D472" t="inlineStr">
         <is>
-          <t>David Bailey</t>
+          <t>Sarah Breeden</t>
         </is>
       </c>
       <c r="E472" t="inlineStr">
         <is>
-          <t>Strong and Simple – completing the picture - speech by David Bailey</t>
+          <t>Engaging with the machine: AI and financial stability − speech by Sarah Breeden</t>
         </is>
       </c>
       <c r="F472" t="inlineStr">
         <is>
-          <t>https://www.bankofengland.co.uk/speech/2024/september/david-bailey-speech-at-building-societies-association</t>
+          <t>https://www.bankofengland.co.uk/speech/2024/october/sarah-breeden-keynote-speech-at-the-hong-kong-monetary-authority</t>
         </is>
       </c>
       <c r="G472" t="n">
-        <v>29318</v>
+        <v>25976</v>
       </c>
       <c r="H472" t="inlineStr">
         <is>
-          <t>bodies\BOE_2026-05-29_c3aaf9ec.txt</t>
+          <t>bodies\BOE_2026-05-21_b01380a3.txt</t>
         </is>
       </c>
     </row>
     <row r="473">
       <c r="A473" t="inlineStr">
         <is>
-          <t>BOE_2026-06-02_8d2dbe08</t>
+          <t>BOE_2026-06-02_8b889139</t>
         </is>
       </c>
       <c r="B473" t="inlineStr">
@@ -19312,37 +19312,37 @@
       </c>
       <c r="D473" t="inlineStr">
         <is>
-          <t>Megan Greene</t>
+          <t>Swati Dhingra</t>
         </is>
       </c>
       <c r="E473" t="inlineStr">
         <is>
-          <t>Who’s buying? The outlook for consumption in a rate cutting cycle − speech by Megan Greene</t>
+          <t>Monetary Policy: Lessons from the pandemic - slides by Swati Dhingra</t>
         </is>
       </c>
       <c r="F473" t="inlineStr">
         <is>
-          <t>https://www.bankofengland.co.uk/speech/2024/september/megan-greene-speech-on-consumption-hosted-by-the-chambers-of-commerce-newcastle</t>
+          <t>https://www.bankofengland.co.uk/speech/2024/october/swati-dhingra-panellist-at-the-reserve-bank-of-india-conference</t>
         </is>
       </c>
       <c r="G473" t="n">
-        <v>38924</v>
+        <v>3490</v>
       </c>
       <c r="H473" t="inlineStr">
         <is>
-          <t>bodies\BOE_2026-06-02_8d2dbe08.txt</t>
+          <t>bodies\BOE_2026-06-02_8b889139.txt</t>
         </is>
       </c>
     </row>
     <row r="474">
       <c r="A474" t="inlineStr">
         <is>
-          <t>BOE_2026-05-29_82cb0f3f</t>
+          <t>BOE_2026-06-02_d99dbee5</t>
         </is>
       </c>
       <c r="B474" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="C474" t="inlineStr">
@@ -19352,37 +19352,37 @@
       </c>
       <c r="D474" t="inlineStr">
         <is>
-          <t>Sarah Breeden</t>
+          <t>Catherine L. Mann</t>
         </is>
       </c>
       <c r="E474" t="inlineStr">
         <is>
-          <t>Financial stability at your service − speech by Sarah Breeden</t>
+          <t>Policy spillovers when external shocks persist and domestic activity diverges - speech by Catherine L. Mann</t>
         </is>
       </c>
       <c r="F474" t="inlineStr">
         <is>
-          <t>https://www.bankofengland.co.uk/speech/2024/september/sarah-breeden-remarks-from-the-wharton-imf-transatlantic-dialogue</t>
+          <t>https://www.bankofengland.co.uk/speech/2024/september/catherine-l-mann-keynote-speech-at-the-central-bank-research-association</t>
         </is>
       </c>
       <c r="G474" t="n">
-        <v>47294</v>
+        <v>39410</v>
       </c>
       <c r="H474" t="inlineStr">
         <is>
-          <t>bodies\BOE_2026-05-29_82cb0f3f.txt</t>
+          <t>bodies\BOE_2026-06-02_d99dbee5.txt</t>
         </is>
       </c>
     </row>
     <row r="475">
       <c r="A475" t="inlineStr">
         <is>
-          <t>BOE_2024-01-01_b61b3205</t>
+          <t>BOE_2026-05-29_c3aaf9ec</t>
         </is>
       </c>
       <c r="B475" t="inlineStr">
         <is>
-          <t>2024-01-01</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="C475" t="inlineStr">
@@ -19392,37 +19392,37 @@
       </c>
       <c r="D475" t="inlineStr">
         <is>
-          <t>Megan Greene</t>
+          <t>David Bailey</t>
         </is>
       </c>
       <c r="E475" t="inlineStr">
         <is>
-          <t>Two puzzles: recent UK labour market dynamics − speech by Megan Greene(pdf 0.4MB)</t>
+          <t>Strong and Simple – completing the picture - speech by David Bailey</t>
         </is>
       </c>
       <c r="F475" t="inlineStr">
         <is>
-          <t>https://www.bankofengland.co.uk/-/media/boe/files/speech/2024/may/two-puzzles-recent-uk-labour-market dynamics-speech-by-megan-greene-appendix.pdf</t>
+          <t>https://www.bankofengland.co.uk/speech/2024/september/david-bailey-speech-at-building-societies-association</t>
         </is>
       </c>
       <c r="G475" t="n">
-        <v>80639</v>
+        <v>29318</v>
       </c>
       <c r="H475" t="inlineStr">
         <is>
-          <t>bodies\BOE_2024-01-01_b61b3205.txt</t>
+          <t>bodies\BOE_2026-05-29_c3aaf9ec.txt</t>
         </is>
       </c>
     </row>
     <row r="476">
       <c r="A476" t="inlineStr">
         <is>
-          <t>BOE_2026-06-25_da6095af</t>
+          <t>BOE_2026-06-02_8d2dbe08</t>
         </is>
       </c>
       <c r="B476" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="C476" t="inlineStr">
@@ -19432,37 +19432,37 @@
       </c>
       <c r="D476" t="inlineStr">
         <is>
-          <t>Dave Ramsden</t>
+          <t>Megan Greene</t>
         </is>
       </c>
       <c r="E476" t="inlineStr">
         <is>
-          <t>Renewed RTGS: Digital public infrastructure as a platform for innovation − speech by Dave Ramsden</t>
+          <t>Who’s buying? The outlook for consumption in a rate cutting cycle − speech by Megan Greene</t>
         </is>
       </c>
       <c r="F476" t="inlineStr">
         <is>
-          <t>https://www.bankofengland.co.uk/speech/2025/april/dave-ramsden-keynote-speech-at-innovate-finance-global-summit</t>
+          <t>https://www.bankofengland.co.uk/speech/2024/september/megan-greene-speech-on-consumption-hosted-by-the-chambers-of-commerce-newcastle</t>
         </is>
       </c>
       <c r="G476" t="n">
-        <v>15829</v>
+        <v>38924</v>
       </c>
       <c r="H476" t="inlineStr">
         <is>
-          <t>bodies\BOE_2026-06-25_da6095af.txt</t>
+          <t>bodies\BOE_2026-06-02_8d2dbe08.txt</t>
         </is>
       </c>
     </row>
     <row r="477">
       <c r="A477" t="inlineStr">
         <is>
-          <t>BOE_2026-06-25_dcaeaafa</t>
+          <t>BOE_2026-05-29_82cb0f3f</t>
         </is>
       </c>
       <c r="B477" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="C477" t="inlineStr">
@@ -19472,37 +19472,37 @@
       </c>
       <c r="D477" t="inlineStr">
         <is>
-          <t>Catherine L. Mann</t>
+          <t>Sarah Breeden</t>
         </is>
       </c>
       <c r="E477" t="inlineStr">
         <is>
-          <t>Five ‘C’s for Central Bank Research − speech by Catherine L. Mann</t>
+          <t>Financial stability at your service − speech by Sarah Breeden</t>
         </is>
       </c>
       <c r="F477" t="inlineStr">
         <is>
-          <t>https://www.bankofengland.co.uk/speech/2025/august/catherine-l-mann-panellist-at-conference-commemorating-100th-anniversary-founding-banco-de-mexico</t>
+          <t>https://www.bankofengland.co.uk/speech/2024/september/sarah-breeden-remarks-from-the-wharton-imf-transatlantic-dialogue</t>
         </is>
       </c>
       <c r="G477" t="n">
-        <v>30123</v>
+        <v>47294</v>
       </c>
       <c r="H477" t="inlineStr">
         <is>
-          <t>bodies\BOE_2026-06-25_dcaeaafa.txt</t>
+          <t>bodies\BOE_2026-05-29_82cb0f3f.txt</t>
         </is>
       </c>
     </row>
     <row r="478">
       <c r="A478" t="inlineStr">
         <is>
-          <t>BOE_2026-06-25_52065aac</t>
+          <t>BOE_2024-01-01_b61b3205</t>
         </is>
       </c>
       <c r="B478" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2024-01-01</t>
         </is>
       </c>
       <c r="C478" t="inlineStr">
@@ -19512,32 +19512,32 @@
       </c>
       <c r="D478" t="inlineStr">
         <is>
-          <t>Andrew Bailey</t>
+          <t>Megan Greene</t>
         </is>
       </c>
       <c r="E478" t="inlineStr">
         <is>
-          <t>Are we underestimating changes in financial markets? - speech by Andrew Bailey</t>
+          <t>Two puzzles: recent UK labour market dynamics − speech by Megan Greene(pdf 0.4MB)</t>
         </is>
       </c>
       <c r="F478" t="inlineStr">
         <is>
-          <t>https://www.bankofengland.co.uk/speech/2025/february/andrew-bailey-keynote-speech-university-of-chicago-booth-school-of-business</t>
+          <t>https://www.bankofengland.co.uk/-/media/boe/files/speech/2024/may/two-puzzles-recent-uk-labour-market dynamics-speech-by-megan-greene-appendix.pdf</t>
         </is>
       </c>
       <c r="G478" t="n">
-        <v>25637</v>
+        <v>80639</v>
       </c>
       <c r="H478" t="inlineStr">
         <is>
-          <t>bodies\BOE_2026-06-25_52065aac.txt</t>
+          <t>bodies\BOE_2024-01-01_b61b3205.txt</t>
         </is>
       </c>
     </row>
     <row r="479">
       <c r="A479" t="inlineStr">
         <is>
-          <t>BOE_2026-06-25_cab0caa8</t>
+          <t>BOE_2026-06-25_da6095af</t>
         </is>
       </c>
       <c r="B479" t="inlineStr">
@@ -19552,32 +19552,32 @@
       </c>
       <c r="D479" t="inlineStr">
         <is>
-          <t>Catherine L. Mann</t>
+          <t>Dave Ramsden</t>
         </is>
       </c>
       <c r="E479" t="inlineStr">
         <is>
-          <t>The February 2025 Monetary Policy Report — and my vote - speech by Catherine L. Mann</t>
+          <t>Renewed RTGS: Digital public infrastructure as a platform for innovation − speech by Dave Ramsden</t>
         </is>
       </c>
       <c r="F479" t="inlineStr">
         <is>
-          <t>https://www.bankofengland.co.uk/speech/2025/february/catherine-l-mann-speech-at-leeds-beckett-university-economic-prospects</t>
+          <t>https://www.bankofengland.co.uk/speech/2025/april/dave-ramsden-keynote-speech-at-innovate-finance-global-summit</t>
         </is>
       </c>
       <c r="G479" t="n">
-        <v>19092</v>
+        <v>15829</v>
       </c>
       <c r="H479" t="inlineStr">
         <is>
-          <t>bodies\BOE_2026-06-25_cab0caa8.txt</t>
+          <t>bodies\BOE_2026-06-25_da6095af.txt</t>
         </is>
       </c>
     </row>
     <row r="480">
       <c r="A480" t="inlineStr">
         <is>
-          <t>BOE_2026-06-25_e26d6858</t>
+          <t>BOE_2026-06-25_dcaeaafa</t>
         </is>
       </c>
       <c r="B480" t="inlineStr">
@@ -19592,32 +19592,32 @@
       </c>
       <c r="D480" t="inlineStr">
         <is>
-          <t>Dave Ramsden</t>
+          <t>Catherine L. Mann</t>
         </is>
       </c>
       <c r="E480" t="inlineStr">
         <is>
-          <t>Surveys, forecasts and scenarios: setting UK monetary policy under uncertainty − speech by Dave Ramsden</t>
+          <t>Five ‘C’s for Central Bank Research − speech by Catherine L. Mann</t>
         </is>
       </c>
       <c r="F480" t="inlineStr">
         <is>
-          <t>https://www.bankofengland.co.uk/speech/2025/february/dave-ramsden-keynote-speech-stellenbosch-university-on-monetary-policy-geopolitical-fragmentation</t>
+          <t>https://www.bankofengland.co.uk/speech/2025/august/catherine-l-mann-panellist-at-conference-commemorating-100th-anniversary-founding-banco-de-mexico</t>
         </is>
       </c>
       <c r="G480" t="n">
-        <v>30551</v>
+        <v>30123</v>
       </c>
       <c r="H480" t="inlineStr">
         <is>
-          <t>bodies\BOE_2026-06-25_e26d6858.txt</t>
+          <t>bodies\BOE_2026-06-25_dcaeaafa.txt</t>
         </is>
       </c>
     </row>
     <row r="481">
       <c r="A481" t="inlineStr">
         <is>
-          <t>BOE_2026-06-25_f6a39502</t>
+          <t>BOE_2026-06-25_52065aac</t>
         </is>
       </c>
       <c r="B481" t="inlineStr">
@@ -19632,32 +19632,32 @@
       </c>
       <c r="D481" t="inlineStr">
         <is>
-          <t>Megan Greene</t>
+          <t>Andrew Bailey</t>
         </is>
       </c>
       <c r="E481" t="inlineStr">
         <is>
-          <t>Not such an island after all − speech by Megan Greene</t>
+          <t>Are we underestimating changes in financial markets? - speech by Andrew Bailey</t>
         </is>
       </c>
       <c r="F481" t="inlineStr">
         <is>
-          <t>https://www.bankofengland.co.uk/speech/2025/february/megan-greene-speech-at-the-institute-of-directors</t>
+          <t>https://www.bankofengland.co.uk/speech/2025/february/andrew-bailey-keynote-speech-university-of-chicago-booth-school-of-business</t>
         </is>
       </c>
       <c r="G481" t="n">
-        <v>42689</v>
+        <v>25637</v>
       </c>
       <c r="H481" t="inlineStr">
         <is>
-          <t>bodies\BOE_2026-06-25_f6a39502.txt</t>
+          <t>bodies\BOE_2026-06-25_52065aac.txt</t>
         </is>
       </c>
     </row>
     <row r="482">
       <c r="A482" t="inlineStr">
         <is>
-          <t>BOE_2026-06-25_978b6dd0</t>
+          <t>BOE_2026-06-25_cab0caa8</t>
         </is>
       </c>
       <c r="B482" t="inlineStr">
@@ -19672,32 +19672,32 @@
       </c>
       <c r="D482" t="inlineStr">
         <is>
-          <t>Swati Dhingra</t>
+          <t>Catherine L. Mann</t>
         </is>
       </c>
       <c r="E482" t="inlineStr">
         <is>
-          <t>Between a shock and a hard place: trade fragmentation and monetary policy – speech by Swati Dhingra</t>
+          <t>The February 2025 Monetary Policy Report — and my vote - speech by Catherine L. Mann</t>
         </is>
       </c>
       <c r="F482" t="inlineStr">
         <is>
-          <t>https://www.bankofengland.co.uk/speech/2025/february/swati-dhingra-speech-dow-lecture-niesr-trade-fragmentation-and-monetary-policy</t>
+          <t>https://www.bankofengland.co.uk/speech/2025/february/catherine-l-mann-speech-at-leeds-beckett-university-economic-prospects</t>
         </is>
       </c>
       <c r="G482" t="n">
-        <v>28141</v>
+        <v>19092</v>
       </c>
       <c r="H482" t="inlineStr">
         <is>
-          <t>bodies\BOE_2026-06-25_978b6dd0.txt</t>
+          <t>bodies\BOE_2026-06-25_cab0caa8.txt</t>
         </is>
       </c>
     </row>
     <row r="483">
       <c r="A483" t="inlineStr">
         <is>
-          <t>BOE_2026-06-25_8b388191</t>
+          <t>BOE_2026-06-25_e26d6858</t>
         </is>
       </c>
       <c r="B483" t="inlineStr">
@@ -19712,32 +19712,32 @@
       </c>
       <c r="D483" t="inlineStr">
         <is>
-          <t>Alan Taylor</t>
+          <t>Dave Ramsden</t>
         </is>
       </c>
       <c r="E483" t="inlineStr">
         <is>
-          <t>The last half mile − speech by Alan Taylor</t>
+          <t>Surveys, forecasts and scenarios: setting UK monetary policy under uncertainty − speech by Dave Ramsden</t>
         </is>
       </c>
       <c r="F483" t="inlineStr">
         <is>
-          <t>https://www.bankofengland.co.uk/speech/2025/january/alan-taylor-speech-at-leeds-university-inflation-dynamics-and-outlook</t>
+          <t>https://www.bankofengland.co.uk/speech/2025/february/dave-ramsden-keynote-speech-stellenbosch-university-on-monetary-policy-geopolitical-fragmentation</t>
         </is>
       </c>
       <c r="G483" t="n">
-        <v>42764</v>
+        <v>30551</v>
       </c>
       <c r="H483" t="inlineStr">
         <is>
-          <t>bodies\BOE_2026-06-25_8b388191.txt</t>
+          <t>bodies\BOE_2026-06-25_e26d6858.txt</t>
         </is>
       </c>
     </row>
     <row r="484">
       <c r="A484" t="inlineStr">
         <is>
-          <t>BOE_2026-06-25_ed4ae304</t>
+          <t>BOE_2026-06-25_f6a39502</t>
         </is>
       </c>
       <c r="B484" t="inlineStr">
@@ -19752,32 +19752,32 @@
       </c>
       <c r="D484" t="inlineStr">
         <is>
-          <t>Sarah Breeden</t>
+          <t>Megan Greene</t>
         </is>
       </c>
       <c r="E484" t="inlineStr">
         <is>
-          <t>Reading between the lines − speech by Sarah Breeden</t>
+          <t>Not such an island after all − speech by Megan Greene</t>
         </is>
       </c>
       <c r="F484" t="inlineStr">
         <is>
-          <t>https://www.bankofengland.co.uk/speech/2025/january/sarah-breeden-speech-at-the-university-of-edinburgh</t>
+          <t>https://www.bankofengland.co.uk/speech/2025/february/megan-greene-speech-at-the-institute-of-directors</t>
         </is>
       </c>
       <c r="G484" t="n">
-        <v>32087</v>
+        <v>42689</v>
       </c>
       <c r="H484" t="inlineStr">
         <is>
-          <t>bodies\BOE_2026-06-25_ed4ae304.txt</t>
+          <t>bodies\BOE_2026-06-25_f6a39502.txt</t>
         </is>
       </c>
     </row>
     <row r="485">
       <c r="A485" t="inlineStr">
         <is>
-          <t>BOE_2026-06-25_0453af99</t>
+          <t>BOE_2026-06-25_978b6dd0</t>
         </is>
       </c>
       <c r="B485" t="inlineStr">
@@ -19792,37 +19792,37 @@
       </c>
       <c r="D485" t="inlineStr">
         <is>
-          <t>Alan Taylor</t>
+          <t>Swati Dhingra</t>
         </is>
       </c>
       <c r="E485" t="inlineStr">
         <is>
-          <t>Unexpected curves − remarks by Alan Taylor</t>
+          <t>Between a shock and a hard place: trade fragmentation and monetary policy – speech by Swati Dhingra</t>
         </is>
       </c>
       <c r="F485" t="inlineStr">
         <is>
-          <t>https://www.bankofengland.co.uk/speech/2025/july/alan-taylor-panellist-at-ecb-forum-on-central-banking-2025</t>
+          <t>https://www.bankofengland.co.uk/speech/2025/february/swati-dhingra-speech-dow-lecture-niesr-trade-fragmentation-and-monetary-policy</t>
         </is>
       </c>
       <c r="G485" t="n">
-        <v>27186</v>
+        <v>28141</v>
       </c>
       <c r="H485" t="inlineStr">
         <is>
-          <t>bodies\BOE_2026-06-25_0453af99.txt</t>
+          <t>bodies\BOE_2026-06-25_978b6dd0.txt</t>
         </is>
       </c>
     </row>
     <row r="486">
       <c r="A486" t="inlineStr">
         <is>
-          <t>BOE_2026-06-24_73730f5a</t>
+          <t>BOE_2026-06-25_8b388191</t>
         </is>
       </c>
       <c r="B486" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="C486" t="inlineStr">
@@ -19837,27 +19837,27 @@
       </c>
       <c r="E486" t="inlineStr">
         <is>
-          <t>The end of the road − speech by Alan Taylor</t>
+          <t>The last half mile − speech by Alan Taylor</t>
         </is>
       </c>
       <c r="F486" t="inlineStr">
         <is>
-          <t>https://www.bankofengland.co.uk/speech/2025/july/alan-taylor-speech-at-the-london-school-of-economics-and-political-science-public-lecture</t>
+          <t>https://www.bankofengland.co.uk/speech/2025/january/alan-taylor-speech-at-leeds-university-inflation-dynamics-and-outlook</t>
         </is>
       </c>
       <c r="G486" t="n">
-        <v>44192</v>
+        <v>42764</v>
       </c>
       <c r="H486" t="inlineStr">
         <is>
-          <t>bodies\BOE_2026-06-24_73730f5a.txt</t>
+          <t>bodies\BOE_2026-06-25_8b388191.txt</t>
         </is>
       </c>
     </row>
     <row r="487">
       <c r="A487" t="inlineStr">
         <is>
-          <t>BOE_2026-06-25_08e0f94c</t>
+          <t>BOE_2026-06-25_ed4ae304</t>
         </is>
       </c>
       <c r="B487" t="inlineStr">
@@ -19872,32 +19872,32 @@
       </c>
       <c r="D487" t="inlineStr">
         <is>
-          <t>Andrew Bailey</t>
+          <t>Sarah Breeden</t>
         </is>
       </c>
       <c r="E487" t="inlineStr">
         <is>
-          <t>The meaning of reserve currency − remarks by Andrew Bailey</t>
+          <t>Reading between the lines − speech by Sarah Breeden</t>
         </is>
       </c>
       <c r="F487" t="inlineStr">
         <is>
-          <t>https://www.bankofengland.co.uk/speech/2025/july/meaning-of-reserve-currency-remarks-andrew-bailey</t>
+          <t>https://www.bankofengland.co.uk/speech/2025/january/sarah-breeden-speech-at-the-university-of-edinburgh</t>
         </is>
       </c>
       <c r="G487" t="n">
-        <v>6860</v>
+        <v>32087</v>
       </c>
       <c r="H487" t="inlineStr">
         <is>
-          <t>bodies\BOE_2026-06-25_08e0f94c.txt</t>
+          <t>bodies\BOE_2026-06-25_ed4ae304.txt</t>
         </is>
       </c>
     </row>
     <row r="488">
       <c r="A488" t="inlineStr">
         <is>
-          <t>BOE_2026-06-25_1e70a76a</t>
+          <t>BOE_2026-06-25_0453af99</t>
         </is>
       </c>
       <c r="B488" t="inlineStr">
@@ -19912,37 +19912,37 @@
       </c>
       <c r="D488" t="inlineStr">
         <is>
-          <t>Andrew Bailey</t>
+          <t>Alan Taylor</t>
         </is>
       </c>
       <c r="E488" t="inlineStr">
         <is>
-          <t>The UK economy in an unpredictable world – speech by Andrew Bailey</t>
+          <t>Unexpected curves − remarks by Alan Taylor</t>
         </is>
       </c>
       <c r="F488" t="inlineStr">
         <is>
-          <t>https://www.bankofengland.co.uk/speech/2025/june/andrew-bailey-keynote-speech-at-the-british-chambers-of-commerce-global-annual-conference</t>
+          <t>https://www.bankofengland.co.uk/speech/2025/july/alan-taylor-panellist-at-ecb-forum-on-central-banking-2025</t>
         </is>
       </c>
       <c r="G488" t="n">
-        <v>16745</v>
+        <v>27186</v>
       </c>
       <c r="H488" t="inlineStr">
         <is>
-          <t>bodies\BOE_2026-06-25_1e70a76a.txt</t>
+          <t>bodies\BOE_2026-06-25_0453af99.txt</t>
         </is>
       </c>
     </row>
     <row r="489">
       <c r="A489" t="inlineStr">
         <is>
-          <t>BOE_2026-06-25_10d160b7</t>
+          <t>BOE_2026-06-24_73730f5a</t>
         </is>
       </c>
       <c r="B489" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="C489" t="inlineStr">
@@ -19952,32 +19952,32 @@
       </c>
       <c r="D489" t="inlineStr">
         <is>
-          <t>Andrew Bailey</t>
+          <t>Alan Taylor</t>
         </is>
       </c>
       <c r="E489" t="inlineStr">
         <is>
-          <t>Revisiting the Norman Conquest of $4.86. Thoughts for the world today - speech by Andrew Bailey</t>
+          <t>The end of the road − speech by Alan Taylor</t>
         </is>
       </c>
       <c r="F489" t="inlineStr">
         <is>
-          <t>https://www.bankofengland.co.uk/speech/2025/june/andrew-bailey-opening-remarks-at-britains-return-to-the-gold-standard-in-1925-conference</t>
+          <t>https://www.bankofengland.co.uk/speech/2025/july/alan-taylor-speech-at-the-london-school-of-economics-and-political-science-public-lecture</t>
         </is>
       </c>
       <c r="G489" t="n">
-        <v>12454</v>
+        <v>44192</v>
       </c>
       <c r="H489" t="inlineStr">
         <is>
-          <t>bodies\BOE_2026-06-25_10d160b7.txt</t>
+          <t>bodies\BOE_2026-06-24_73730f5a.txt</t>
         </is>
       </c>
     </row>
     <row r="490">
       <c r="A490" t="inlineStr">
         <is>
-          <t>BOE_2026-06-25_9f141eb5</t>
+          <t>BOE_2026-06-25_08e0f94c</t>
         </is>
       </c>
       <c r="B490" t="inlineStr">
@@ -19997,27 +19997,27 @@
       </c>
       <c r="E490" t="inlineStr">
         <is>
-          <t>Central Banking in extreme adversity - speech by Andrew Bailey</t>
+          <t>The meaning of reserve currency − remarks by Andrew Bailey</t>
         </is>
       </c>
       <c r="F490" t="inlineStr">
         <is>
-          <t>https://www.bankofengland.co.uk/speech/2025/june/andrew-bailey-speech-at-the-annual-research-conference-kyiv</t>
+          <t>https://www.bankofengland.co.uk/speech/2025/july/meaning-of-reserve-currency-remarks-andrew-bailey</t>
         </is>
       </c>
       <c r="G490" t="n">
-        <v>17136</v>
+        <v>6860</v>
       </c>
       <c r="H490" t="inlineStr">
         <is>
-          <t>bodies\BOE_2026-06-25_9f141eb5.txt</t>
+          <t>bodies\BOE_2026-06-25_08e0f94c.txt</t>
         </is>
       </c>
     </row>
     <row r="491">
       <c r="A491" t="inlineStr">
         <is>
-          <t>BOE_2026-06-25_ae28378c</t>
+          <t>BOE_2026-06-25_1e70a76a</t>
         </is>
       </c>
       <c r="B491" t="inlineStr">
@@ -20032,32 +20032,32 @@
       </c>
       <c r="D491" t="inlineStr">
         <is>
-          <t>Catherine L. Mann</t>
+          <t>Andrew Bailey</t>
         </is>
       </c>
       <c r="E491" t="inlineStr">
         <is>
-          <t>Quantitative tightening and monetary policy stance − speech by Catherine L. Mann</t>
+          <t>The UK economy in an unpredictable world – speech by Andrew Bailey</t>
         </is>
       </c>
       <c r="F491" t="inlineStr">
         <is>
-          <t>https://www.bankofengland.co.uk/speech/2025/june/catherine-l-mann-fireside-chat-at-the-federal-reserve-board-of-governors</t>
+          <t>https://www.bankofengland.co.uk/speech/2025/june/andrew-bailey-keynote-speech-at-the-british-chambers-of-commerce-global-annual-conference</t>
         </is>
       </c>
       <c r="G491" t="n">
-        <v>49089</v>
+        <v>16745</v>
       </c>
       <c r="H491" t="inlineStr">
         <is>
-          <t>bodies\BOE_2026-06-25_ae28378c.txt</t>
+          <t>bodies\BOE_2026-06-25_1e70a76a.txt</t>
         </is>
       </c>
     </row>
     <row r="492">
       <c r="A492" t="inlineStr">
         <is>
-          <t>BOE_2026-06-25_9ba66ee0</t>
+          <t>BOE_2026-06-25_10d160b7</t>
         </is>
       </c>
       <c r="B492" t="inlineStr">
@@ -20072,32 +20072,32 @@
       </c>
       <c r="D492" t="inlineStr">
         <is>
-          <t>Dave Ramsden</t>
+          <t>Andrew Bailey</t>
         </is>
       </c>
       <c r="E492" t="inlineStr">
         <is>
-          <t>Navigating an uncertain outlook: the signals from the labour market − speech by Dave Ramsden</t>
+          <t>Revisiting the Norman Conquest of $4.86. Thoughts for the world today - speech by Andrew Bailey</t>
         </is>
       </c>
       <c r="F492" t="inlineStr">
         <is>
-          <t>https://www.bankofengland.co.uk/speech/2025/june/dave-ramsden-speech-and-panellist-at-the-barclays-cepr-monetary-policy-forum-2025</t>
+          <t>https://www.bankofengland.co.uk/speech/2025/june/andrew-bailey-opening-remarks-at-britains-return-to-the-gold-standard-in-1925-conference</t>
         </is>
       </c>
       <c r="G492" t="n">
-        <v>20047</v>
+        <v>12454</v>
       </c>
       <c r="H492" t="inlineStr">
         <is>
-          <t>bodies\BOE_2026-06-25_9ba66ee0.txt</t>
+          <t>bodies\BOE_2026-06-25_10d160b7.txt</t>
         </is>
       </c>
     </row>
     <row r="493">
       <c r="A493" t="inlineStr">
         <is>
-          <t>BOE_2026-06-25_56e58f3a</t>
+          <t>BOE_2026-06-25_9f141eb5</t>
         </is>
       </c>
       <c r="B493" t="inlineStr">
@@ -20112,37 +20112,37 @@
       </c>
       <c r="D493" t="inlineStr">
         <is>
-          <t>Megan Greene</t>
+          <t>Andrew Bailey</t>
         </is>
       </c>
       <c r="E493" t="inlineStr">
         <is>
-          <t>A feature not a bug − speech by Megan Greene</t>
+          <t>Central Banking in extreme adversity - speech by Andrew Bailey</t>
         </is>
       </c>
       <c r="F493" t="inlineStr">
         <is>
-          <t>https://www.bankofengland.co.uk/speech/2025/june/megan-greene-speech-at-niesr-monetary-policy-implications-of-differences-in-central-bank-balance</t>
+          <t>https://www.bankofengland.co.uk/speech/2025/june/andrew-bailey-speech-at-the-annual-research-conference-kyiv</t>
         </is>
       </c>
       <c r="G493" t="n">
-        <v>46788</v>
+        <v>17136</v>
       </c>
       <c r="H493" t="inlineStr">
         <is>
-          <t>bodies\BOE_2026-06-25_56e58f3a.txt</t>
+          <t>bodies\BOE_2026-06-25_9f141eb5.txt</t>
         </is>
       </c>
     </row>
     <row r="494">
       <c r="A494" t="inlineStr">
         <is>
-          <t>BOE_2026-06-24_1033763d</t>
+          <t>BOE_2026-06-25_ae28378c</t>
         </is>
       </c>
       <c r="B494" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="C494" t="inlineStr">
@@ -20152,37 +20152,37 @@
       </c>
       <c r="D494" t="inlineStr">
         <is>
-          <t>Andrew Bailey</t>
+          <t>Catherine L. Mann</t>
         </is>
       </c>
       <c r="E494" t="inlineStr">
         <is>
-          <t>Growth: What does it take in today’s world? - Lecture by Andrew Bailey</t>
+          <t>Quantitative tightening and monetary policy stance − speech by Catherine L. Mann</t>
         </is>
       </c>
       <c r="F494" t="inlineStr">
         <is>
-          <t>https://www.bankofengland.co.uk/speech/2025/march/andrew-bailey-university-of-leicester-chancellors-distinguished-lecture</t>
+          <t>https://www.bankofengland.co.uk/speech/2025/june/catherine-l-mann-fireside-chat-at-the-federal-reserve-board-of-governors</t>
         </is>
       </c>
       <c r="G494" t="n">
-        <v>37259</v>
+        <v>49089</v>
       </c>
       <c r="H494" t="inlineStr">
         <is>
-          <t>bodies\BOE_2026-06-24_1033763d.txt</t>
+          <t>bodies\BOE_2026-06-25_ae28378c.txt</t>
         </is>
       </c>
     </row>
     <row r="495">
       <c r="A495" t="inlineStr">
         <is>
-          <t>BOE_2026-06-24_65ba130f</t>
+          <t>BOE_2026-06-25_9ba66ee0</t>
         </is>
       </c>
       <c r="B495" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="C495" t="inlineStr">
@@ -20192,32 +20192,32 @@
       </c>
       <c r="D495" t="inlineStr">
         <is>
-          <t>Catherine L. Mann</t>
+          <t>Dave Ramsden</t>
         </is>
       </c>
       <c r="E495" t="inlineStr">
         <is>
-          <t>Holding the anchor in turbulent waters – speech by Catherine L. Mann</t>
+          <t>Navigating an uncertain outlook: the signals from the labour market − speech by Dave Ramsden</t>
         </is>
       </c>
       <c r="F495" t="inlineStr">
         <is>
-          <t>https://www.bankofengland.co.uk/speech/2025/march/catherine-l-mann-keynote-lecture-reserve-bank-of-new-zealand-research-conference</t>
+          <t>https://www.bankofengland.co.uk/speech/2025/june/dave-ramsden-speech-and-panellist-at-the-barclays-cepr-monetary-policy-forum-2025</t>
         </is>
       </c>
       <c r="G495" t="n">
-        <v>53397</v>
+        <v>20047</v>
       </c>
       <c r="H495" t="inlineStr">
         <is>
-          <t>bodies\BOE_2026-06-24_65ba130f.txt</t>
+          <t>bodies\BOE_2026-06-25_9ba66ee0.txt</t>
         </is>
       </c>
     </row>
     <row r="496">
       <c r="A496" t="inlineStr">
         <is>
-          <t>BOE_2026-06-25_ab1f2429</t>
+          <t>BOE_2026-06-25_56e58f3a</t>
         </is>
       </c>
       <c r="B496" t="inlineStr">
@@ -20232,37 +20232,37 @@
       </c>
       <c r="D496" t="inlineStr">
         <is>
-          <t>Andrew Bailey</t>
+          <t>Megan Greene</t>
         </is>
       </c>
       <c r="E496" t="inlineStr">
         <is>
-          <t>Monetary policy in uncertain times - speech by Andrew Bailey</t>
+          <t>A feature not a bug − speech by Megan Greene</t>
         </is>
       </c>
       <c r="F496" t="inlineStr">
         <is>
-          <t>https://www.bankofengland.co.uk/speech/2025/may/andrew-bailey-keynote-address-at-the-reykjavik-economic-conference-2025</t>
+          <t>https://www.bankofengland.co.uk/speech/2025/june/megan-greene-speech-at-niesr-monetary-policy-implications-of-differences-in-central-bank-balance</t>
         </is>
       </c>
       <c r="G496" t="n">
-        <v>16082</v>
+        <v>46788</v>
       </c>
       <c r="H496" t="inlineStr">
         <is>
-          <t>bodies\BOE_2026-06-25_ab1f2429.txt</t>
+          <t>bodies\BOE_2026-06-25_56e58f3a.txt</t>
         </is>
       </c>
     </row>
     <row r="497">
       <c r="A497" t="inlineStr">
         <is>
-          <t>BOE_2026-06-25_d2361b6f</t>
+          <t>BOE_2026-06-24_1033763d</t>
         </is>
       </c>
       <c r="B497" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="C497" t="inlineStr">
@@ -20277,32 +20277,32 @@
       </c>
       <c r="E497" t="inlineStr">
         <is>
-          <t>State of trade - speech by Andrew Bailey</t>
+          <t>Growth: What does it take in today’s world? - Lecture by Andrew Bailey</t>
         </is>
       </c>
       <c r="F497" t="inlineStr">
         <is>
-          <t>https://www.bankofengland.co.uk/speech/2025/may/andrew-bailey-speech-followed-by-fireside-chat-with-francine-lacqua-bloomberg</t>
+          <t>https://www.bankofengland.co.uk/speech/2025/march/andrew-bailey-university-of-leicester-chancellors-distinguished-lecture</t>
         </is>
       </c>
       <c r="G497" t="n">
-        <v>15853</v>
+        <v>37259</v>
       </c>
       <c r="H497" t="inlineStr">
         <is>
-          <t>bodies\BOE_2026-06-25_d2361b6f.txt</t>
+          <t>bodies\BOE_2026-06-24_1033763d.txt</t>
         </is>
       </c>
     </row>
     <row r="498">
       <c r="A498" t="inlineStr">
         <is>
-          <t>BOE_2026-06-25_00a045b7</t>
+          <t>BOE_2026-06-24_65ba130f</t>
         </is>
       </c>
       <c r="B498" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="C498" t="inlineStr">
@@ -20312,32 +20312,32 @@
       </c>
       <c r="D498" t="inlineStr">
         <is>
-          <t>Clare Lombardelli</t>
+          <t>Catherine L. Mann</t>
         </is>
       </c>
       <c r="E498" t="inlineStr">
         <is>
-          <t>Central bank communications and uncertainty - remarks by Clare Lombardelli</t>
+          <t>Holding the anchor in turbulent waters – speech by Catherine L. Mann</t>
         </is>
       </c>
       <c r="F498" t="inlineStr">
         <is>
-          <t>https://www.bankofengland.co.uk/speech/2025/may/central-bank-communications-and-uncertainty-remarks-by-clare-lombardelli</t>
+          <t>https://www.bankofengland.co.uk/speech/2025/march/catherine-l-mann-keynote-lecture-reserve-bank-of-new-zealand-research-conference</t>
         </is>
       </c>
       <c r="G498" t="n">
-        <v>9573</v>
+        <v>53397</v>
       </c>
       <c r="H498" t="inlineStr">
         <is>
-          <t>bodies\BOE_2026-06-25_00a045b7.txt</t>
+          <t>bodies\BOE_2026-06-24_65ba130f.txt</t>
         </is>
       </c>
     </row>
     <row r="499">
       <c r="A499" t="inlineStr">
         <is>
-          <t>BOE_2026-06-25_38d9518f</t>
+          <t>BOE_2026-06-25_ab1f2429</t>
         </is>
       </c>
       <c r="B499" t="inlineStr">
@@ -20352,32 +20352,32 @@
       </c>
       <c r="D499" t="inlineStr">
         <is>
-          <t>Clare Lombardelli</t>
+          <t>Andrew Bailey</t>
         </is>
       </c>
       <c r="E499" t="inlineStr">
         <is>
-          <t>What if things are different? - speech by Clare Lombardelli</t>
+          <t>Monetary policy in uncertain times - speech by Andrew Bailey</t>
         </is>
       </c>
       <c r="F499" t="inlineStr">
         <is>
-          <t>https://www.bankofengland.co.uk/speech/2025/may/clare-lombardelli-keynote-speech-at-the-bank-of-england-bank-watchers-conference</t>
+          <t>https://www.bankofengland.co.uk/speech/2025/may/andrew-bailey-keynote-address-at-the-reykjavik-economic-conference-2025</t>
         </is>
       </c>
       <c r="G499" t="n">
-        <v>20905</v>
+        <v>16082</v>
       </c>
       <c r="H499" t="inlineStr">
         <is>
-          <t>bodies\BOE_2026-06-25_38d9518f.txt</t>
+          <t>bodies\BOE_2026-06-25_ab1f2429.txt</t>
         </is>
       </c>
     </row>
     <row r="500">
       <c r="A500" t="inlineStr">
         <is>
-          <t>BOE_2026-06-25_319c0475</t>
+          <t>BOE_2026-06-25_d2361b6f</t>
         </is>
       </c>
       <c r="B500" t="inlineStr">
@@ -20392,32 +20392,32 @@
       </c>
       <c r="D500" t="inlineStr">
         <is>
-          <t>Huw Pill</t>
+          <t>Andrew Bailey</t>
         </is>
       </c>
       <c r="E500" t="inlineStr">
         <is>
-          <t>The courage not to act − remarks by Huw Pill</t>
+          <t>State of trade - speech by Andrew Bailey</t>
         </is>
       </c>
       <c r="F500" t="inlineStr">
         <is>
-          <t>https://www.bankofengland.co.uk/speech/2025/may/huw-pill-speech-at-the-barclays-briefing</t>
+          <t>https://www.bankofengland.co.uk/speech/2025/may/andrew-bailey-speech-followed-by-fireside-chat-with-francine-lacqua-bloomberg</t>
         </is>
       </c>
       <c r="G500" t="n">
-        <v>1247</v>
+        <v>15853</v>
       </c>
       <c r="H500" t="inlineStr">
         <is>
-          <t>bodies\BOE_2026-06-25_319c0475.txt</t>
+          <t>bodies\BOE_2026-06-25_d2361b6f.txt</t>
         </is>
       </c>
     </row>
     <row r="501">
       <c r="A501" t="inlineStr">
         <is>
-          <t>BOE_2026-06-25_1f89a919</t>
+          <t>BOE_2026-06-25_00a045b7</t>
         </is>
       </c>
       <c r="B501" t="inlineStr">
@@ -20432,32 +20432,32 @@
       </c>
       <c r="D501" t="inlineStr">
         <is>
-          <t>Megan Greene</t>
+          <t>Clare Lombardelli</t>
         </is>
       </c>
       <c r="E501" t="inlineStr">
         <is>
-          <t>Monetary policy outlook - slides by Megan Greene</t>
+          <t>Central bank communications and uncertainty - remarks by Clare Lombardelli</t>
         </is>
       </c>
       <c r="F501" t="inlineStr">
         <is>
-          <t>https://www.bankofengland.co.uk/speech/2025/may/megan-greene-panellist-at-the-bank-of-england-bank-watchers-conference</t>
+          <t>https://www.bankofengland.co.uk/speech/2025/may/central-bank-communications-and-uncertainty-remarks-by-clare-lombardelli</t>
         </is>
       </c>
       <c r="G501" t="n">
-        <v>14749</v>
+        <v>9573</v>
       </c>
       <c r="H501" t="inlineStr">
         <is>
-          <t>bodies\BOE_2026-06-25_1f89a919.txt</t>
+          <t>bodies\BOE_2026-06-25_00a045b7.txt</t>
         </is>
       </c>
     </row>
     <row r="502">
       <c r="A502" t="inlineStr">
         <is>
-          <t>BOE_2026-06-25_e950cd1a</t>
+          <t>BOE_2026-06-25_38d9518f</t>
         </is>
       </c>
       <c r="B502" t="inlineStr">
@@ -20472,32 +20472,32 @@
       </c>
       <c r="D502" t="inlineStr">
         <is>
-          <t>Sarah Breeden</t>
+          <t>Clare Lombardelli</t>
         </is>
       </c>
       <c r="E502" t="inlineStr">
         <is>
-          <t>A system-wide approach to system-wide resilience:  CCPs and their users − speech by Sarah Breeden</t>
+          <t>What if things are different? - speech by Clare Lombardelli</t>
         </is>
       </c>
       <c r="F502" t="inlineStr">
         <is>
-          <t>https://www.bankofengland.co.uk/speech/2025/may/sarah-breeden-keynote-address-at-the-international-swaps-and-derivatives-association</t>
+          <t>https://www.bankofengland.co.uk/speech/2025/may/clare-lombardelli-keynote-speech-at-the-bank-of-england-bank-watchers-conference</t>
         </is>
       </c>
       <c r="G502" t="n">
-        <v>18000</v>
+        <v>20905</v>
       </c>
       <c r="H502" t="inlineStr">
         <is>
-          <t>bodies\BOE_2026-06-25_e950cd1a.txt</t>
+          <t>bodies\BOE_2026-06-25_38d9518f.txt</t>
         </is>
       </c>
     </row>
     <row r="503">
       <c r="A503" t="inlineStr">
         <is>
-          <t>BOE_2026-06-25_4c6a8955</t>
+          <t>BOE_2026-06-25_319c0475</t>
         </is>
       </c>
       <c r="B503" t="inlineStr">
@@ -20512,32 +20512,32 @@
       </c>
       <c r="D503" t="inlineStr">
         <is>
-          <t>Swati Dhingra</t>
+          <t>Huw Pill</t>
         </is>
       </c>
       <c r="E503" t="inlineStr">
         <is>
-          <t>EU macroeconomic policy in an age of shocks: a view from the UK - slides by Swati Dhingra</t>
+          <t>The courage not to act − remarks by Huw Pill</t>
         </is>
       </c>
       <c r="F503" t="inlineStr">
         <is>
-          <t>https://www.bankofengland.co.uk/speech/2025/may/swati-dhingra-speech-at-the-new-economics-foundation-conference</t>
+          <t>https://www.bankofengland.co.uk/speech/2025/may/huw-pill-speech-at-the-barclays-briefing</t>
         </is>
       </c>
       <c r="G503" t="n">
-        <v>2207</v>
+        <v>1247</v>
       </c>
       <c r="H503" t="inlineStr">
         <is>
-          <t>bodies\BOE_2026-06-25_4c6a8955.txt</t>
+          <t>bodies\BOE_2026-06-25_319c0475.txt</t>
         </is>
       </c>
     </row>
     <row r="504">
       <c r="A504" t="inlineStr">
         <is>
-          <t>BOE_2026-06-25_eaee8b15</t>
+          <t>BOE_2026-06-25_1f89a919</t>
         </is>
       </c>
       <c r="B504" t="inlineStr">
@@ -20552,32 +20552,32 @@
       </c>
       <c r="D504" t="inlineStr">
         <is>
-          <t>Swati Dhingra</t>
+          <t>Megan Greene</t>
         </is>
       </c>
       <c r="E504" t="inlineStr">
         <is>
-          <t>Unpacking the puzzle of income growth and weak consumption in the UK and other mysteries - slides by Swati Dhingra</t>
+          <t>Monetary policy outlook - slides by Megan Greene</t>
         </is>
       </c>
       <c r="F504" t="inlineStr">
         <is>
-          <t>https://www.bankofengland.co.uk/speech/2025/november/swati-dhingra-speech-at-the-knoop-annual-lecture-held-at-the-university-of-sheffield</t>
+          <t>https://www.bankofengland.co.uk/speech/2025/may/megan-greene-panellist-at-the-bank-of-england-bank-watchers-conference</t>
         </is>
       </c>
       <c r="G504" t="n">
-        <v>12497</v>
+        <v>14749</v>
       </c>
       <c r="H504" t="inlineStr">
         <is>
-          <t>bodies\BOE_2026-06-25_eaee8b15.txt</t>
+          <t>bodies\BOE_2026-06-25_1f89a919.txt</t>
         </is>
       </c>
     </row>
     <row r="505">
       <c r="A505" t="inlineStr">
         <is>
-          <t>BOE_2026-06-25_f5117ba1</t>
+          <t>BOE_2026-06-25_e950cd1a</t>
         </is>
       </c>
       <c r="B505" t="inlineStr">
@@ -20592,32 +20592,32 @@
       </c>
       <c r="D505" t="inlineStr">
         <is>
-          <t>Alan Taylor</t>
+          <t>Sarah Breeden</t>
         </is>
       </c>
       <c r="E505" t="inlineStr">
         <is>
-          <t>Diversion ahead − speech by Alan Taylor</t>
+          <t>A system-wide approach to system-wide resilience:  CCPs and their users − speech by Sarah Breeden</t>
         </is>
       </c>
       <c r="F505" t="inlineStr">
         <is>
-          <t>https://www.bankofengland.co.uk/speech/2025/october/alan-taylor-remarks-and-fireside-chat-with-gillian-tett-at-cambridge</t>
+          <t>https://www.bankofengland.co.uk/speech/2025/may/sarah-breeden-keynote-address-at-the-international-swaps-and-derivatives-association</t>
         </is>
       </c>
       <c r="G505" t="n">
-        <v>36755</v>
+        <v>18000</v>
       </c>
       <c r="H505" t="inlineStr">
         <is>
-          <t>bodies\BOE_2026-06-25_f5117ba1.txt</t>
+          <t>bodies\BOE_2026-06-25_e950cd1a.txt</t>
         </is>
       </c>
     </row>
     <row r="506">
       <c r="A506" t="inlineStr">
         <is>
-          <t>BOE_2026-06-25_1553789f</t>
+          <t>BOE_2026-06-25_4c6a8955</t>
         </is>
       </c>
       <c r="B506" t="inlineStr">
@@ -20632,32 +20632,32 @@
       </c>
       <c r="D506" t="inlineStr">
         <is>
-          <t>Andrew Bailey</t>
+          <t>Swati Dhingra</t>
         </is>
       </c>
       <c r="E506" t="inlineStr">
         <is>
-          <t>Challenges to financial stability - speech by Andrew Bailey</t>
+          <t>EU macroeconomic policy in an age of shocks: a view from the UK - slides by Swati Dhingra</t>
         </is>
       </c>
       <c r="F506" t="inlineStr">
         <is>
-          <t>https://www.bankofengland.co.uk/speech/2025/october/andrew-bailey-keynote-speech-at-klaas-knott-farewell-symposium</t>
+          <t>https://www.bankofengland.co.uk/speech/2025/may/swati-dhingra-speech-at-the-new-economics-foundation-conference</t>
         </is>
       </c>
       <c r="G506" t="n">
-        <v>23944</v>
+        <v>2207</v>
       </c>
       <c r="H506" t="inlineStr">
         <is>
-          <t>bodies\BOE_2026-06-25_1553789f.txt</t>
+          <t>bodies\BOE_2026-06-25_4c6a8955.txt</t>
         </is>
       </c>
     </row>
     <row r="507">
       <c r="A507" t="inlineStr">
         <is>
-          <t>BOE_2026-06-25_8dfe9eb8</t>
+          <t>BOE_2026-06-25_eaee8b15</t>
         </is>
       </c>
       <c r="B507" t="inlineStr">
@@ -20672,32 +20672,32 @@
       </c>
       <c r="D507" t="inlineStr">
         <is>
-          <t>Andrew Bailey</t>
+          <t>Swati Dhingra</t>
         </is>
       </c>
       <c r="E507" t="inlineStr">
         <is>
-          <t>Investment in Scotland - speech by Andrew Bailey</t>
+          <t>Unpacking the puzzle of income growth and weak consumption in the UK and other mysteries - slides by Swati Dhingra</t>
         </is>
       </c>
       <c r="F507" t="inlineStr">
         <is>
-          <t>https://www.bankofengland.co.uk/speech/2025/october/andrew-bailey-keynote-speech-at-scotland-global-investment-summit-2025</t>
+          <t>https://www.bankofengland.co.uk/speech/2025/november/swati-dhingra-speech-at-the-knoop-annual-lecture-held-at-the-university-of-sheffield</t>
         </is>
       </c>
       <c r="G507" t="n">
-        <v>11575</v>
+        <v>12497</v>
       </c>
       <c r="H507" t="inlineStr">
         <is>
-          <t>bodies\BOE_2026-06-25_8dfe9eb8.txt</t>
+          <t>bodies\BOE_2026-06-25_eaee8b15.txt</t>
         </is>
       </c>
     </row>
     <row r="508">
       <c r="A508" t="inlineStr">
         <is>
-          <t>BOE_2026-06-25_d94b1008</t>
+          <t>BOE_2026-06-25_f5117ba1</t>
         </is>
       </c>
       <c r="B508" t="inlineStr">
@@ -20712,32 +20712,32 @@
       </c>
       <c r="D508" t="inlineStr">
         <is>
-          <t>Andrew Bailey</t>
+          <t>Alan Taylor</t>
         </is>
       </c>
       <c r="E508" t="inlineStr">
         <is>
-          <t>Global Economic Outlook Panel – panel remarks by Andrew Bailey</t>
+          <t>Diversion ahead − speech by Alan Taylor</t>
         </is>
       </c>
       <c r="F508" t="inlineStr">
         <is>
-          <t>https://www.bankofengland.co.uk/speech/2025/october/global-economic-outlook-panel-panel-remarks-by-andrew-bailey</t>
+          <t>https://www.bankofengland.co.uk/speech/2025/october/alan-taylor-remarks-and-fireside-chat-with-gillian-tett-at-cambridge</t>
         </is>
       </c>
       <c r="G508" t="n">
-        <v>11819</v>
+        <v>36755</v>
       </c>
       <c r="H508" t="inlineStr">
         <is>
-          <t>bodies\BOE_2026-06-25_d94b1008.txt</t>
+          <t>bodies\BOE_2026-06-25_f5117ba1.txt</t>
         </is>
       </c>
     </row>
     <row r="509">
       <c r="A509" t="inlineStr">
         <is>
-          <t>BOE_2026-06-25_cbee9d70</t>
+          <t>BOE_2026-06-25_1553789f</t>
         </is>
       </c>
       <c r="B509" t="inlineStr">
@@ -20752,32 +20752,32 @@
       </c>
       <c r="D509" t="inlineStr">
         <is>
-          <t>Huw Pill</t>
+          <t>Andrew Bailey</t>
         </is>
       </c>
       <c r="E509" t="inlineStr">
         <is>
-          <t>Evolving UK monetary policy in an evolving world − speech by Huw Pill</t>
+          <t>Challenges to financial stability - speech by Andrew Bailey</t>
         </is>
       </c>
       <c r="F509" t="inlineStr">
         <is>
-          <t>https://www.bankofengland.co.uk/speech/2025/october/huw-pill-speech-at-institute-of-chartered-accountants-in-england-and-wales-annual-conference-2025</t>
+          <t>https://www.bankofengland.co.uk/speech/2025/october/andrew-bailey-keynote-speech-at-klaas-knott-farewell-symposium</t>
         </is>
       </c>
       <c r="G509" t="n">
-        <v>975</v>
+        <v>23944</v>
       </c>
       <c r="H509" t="inlineStr">
         <is>
-          <t>bodies\BOE_2026-06-25_cbee9d70.txt</t>
+          <t>bodies\BOE_2026-06-25_1553789f.txt</t>
         </is>
       </c>
     </row>
     <row r="510">
       <c r="A510" t="inlineStr">
         <is>
-          <t>BOE_2026-06-25_83ceb766</t>
+          <t>BOE_2026-06-25_8dfe9eb8</t>
         </is>
       </c>
       <c r="B510" t="inlineStr">
@@ -20792,32 +20792,32 @@
       </c>
       <c r="D510" t="inlineStr">
         <is>
-          <t>Huw Pill</t>
+          <t>Andrew Bailey</t>
         </is>
       </c>
       <c r="E510" t="inlineStr">
         <is>
-          <t>Uncertainty, structural change and monetary policy strategy - speech by Huw Pill</t>
+          <t>Investment in Scotland - speech by Andrew Bailey</t>
         </is>
       </c>
       <c r="F510" t="inlineStr">
         <is>
-          <t>https://www.bankofengland.co.uk/speech/2025/october/huw-pill-speech-at-the-maxwell-fry-annual-lecture</t>
+          <t>https://www.bankofengland.co.uk/speech/2025/october/andrew-bailey-keynote-speech-at-scotland-global-investment-summit-2025</t>
         </is>
       </c>
       <c r="G510" t="n">
-        <v>15181</v>
+        <v>11575</v>
       </c>
       <c r="H510" t="inlineStr">
         <is>
-          <t>bodies\BOE_2026-06-25_83ceb766.txt</t>
+          <t>bodies\BOE_2026-06-25_8dfe9eb8.txt</t>
         </is>
       </c>
     </row>
     <row r="511">
       <c r="A511" t="inlineStr">
         <is>
-          <t>BOE_2026-06-25_03ae6b31</t>
+          <t>BOE_2026-06-25_d94b1008</t>
         </is>
       </c>
       <c r="B511" t="inlineStr">
@@ -20832,32 +20832,32 @@
       </c>
       <c r="D511" t="inlineStr">
         <is>
-          <t>Sarah Breeden</t>
+          <t>Andrew Bailey</t>
         </is>
       </c>
       <c r="E511" t="inlineStr">
         <is>
-          <t>Not just token gestures − speech by Sarah Breeden</t>
+          <t>Global Economic Outlook Panel – panel remarks by Andrew Bailey</t>
         </is>
       </c>
       <c r="F511" t="inlineStr">
         <is>
-          <t>https://www.bankofengland.co.uk/speech/2025/october/sarah-breeden-panellist-at-fintech-foundation-2025-dc-fiintech-week</t>
+          <t>https://www.bankofengland.co.uk/speech/2025/october/global-economic-outlook-panel-panel-remarks-by-andrew-bailey</t>
         </is>
       </c>
       <c r="G511" t="n">
-        <v>26411</v>
+        <v>11819</v>
       </c>
       <c r="H511" t="inlineStr">
         <is>
-          <t>bodies\BOE_2026-06-25_03ae6b31.txt</t>
+          <t>bodies\BOE_2026-06-25_d94b1008.txt</t>
         </is>
       </c>
     </row>
     <row r="512">
       <c r="A512" t="inlineStr">
         <is>
-          <t>BOE_2026-06-25_20e40f4f</t>
+          <t>BOE_2026-06-25_cbee9d70</t>
         </is>
       </c>
       <c r="B512" t="inlineStr">
@@ -20872,32 +20872,32 @@
       </c>
       <c r="D512" t="inlineStr">
         <is>
-          <t>Swati Dhingra</t>
+          <t>Huw Pill</t>
         </is>
       </c>
       <c r="E512" t="inlineStr">
         <is>
-          <t>Tariffed with the same brush: confronting today’s challenges to trade − speech by Swati Dhingra</t>
+          <t>Evolving UK monetary policy in an evolving world − speech by Huw Pill</t>
         </is>
       </c>
       <c r="F512" t="inlineStr">
         <is>
-          <t>https://www.bankofengland.co.uk/speech/2025/october/swati-dhingra-speech-at-the-central-bank-of-ireland-escb-cluster-2-academic-conference</t>
+          <t>https://www.bankofengland.co.uk/speech/2025/october/huw-pill-speech-at-institute-of-chartered-accountants-in-england-and-wales-annual-conference-2025</t>
         </is>
       </c>
       <c r="G512" t="n">
-        <v>30624</v>
+        <v>975</v>
       </c>
       <c r="H512" t="inlineStr">
         <is>
-          <t>bodies\BOE_2026-06-25_20e40f4f.txt</t>
+          <t>bodies\BOE_2026-06-25_cbee9d70.txt</t>
         </is>
       </c>
     </row>
     <row r="513">
       <c r="A513" t="inlineStr">
         <is>
-          <t>BOE_2026-06-25_fc72e0b8</t>
+          <t>BOE_2026-06-25_83ceb766</t>
         </is>
       </c>
       <c r="B513" t="inlineStr">
@@ -20917,27 +20917,27 @@
       </c>
       <c r="E513" t="inlineStr">
         <is>
-          <t>On QT − remarks by Huw Pill</t>
+          <t>Uncertainty, structural change and monetary policy strategy - speech by Huw Pill</t>
         </is>
       </c>
       <c r="F513" t="inlineStr">
         <is>
-          <t>https://www.bankofengland.co.uk/speech/2025/september/huw-pill-fireside-chat-at-the-inaugural-pictet-research-institute-symposium</t>
+          <t>https://www.bankofengland.co.uk/speech/2025/october/huw-pill-speech-at-the-maxwell-fry-annual-lecture</t>
         </is>
       </c>
       <c r="G513" t="n">
-        <v>8045</v>
+        <v>15181</v>
       </c>
       <c r="H513" t="inlineStr">
         <is>
-          <t>bodies\BOE_2026-06-25_fc72e0b8.txt</t>
+          <t>bodies\BOE_2026-06-25_83ceb766.txt</t>
         </is>
       </c>
     </row>
     <row r="514">
       <c r="A514" t="inlineStr">
         <is>
-          <t>BOE_2026-06-25_f943d34c</t>
+          <t>BOE_2026-06-25_03ae6b31</t>
         </is>
       </c>
       <c r="B514" t="inlineStr">
@@ -20952,32 +20952,32 @@
       </c>
       <c r="D514" t="inlineStr">
         <is>
-          <t>Megan Greene</t>
+          <t>Sarah Breeden</t>
         </is>
       </c>
       <c r="E514" t="inlineStr">
         <is>
-          <t>The supply side demands more attention − speech by Megan Greene</t>
+          <t>Not just token gestures − speech by Sarah Breeden</t>
         </is>
       </c>
       <c r="F514" t="inlineStr">
         <is>
-          <t>https://www.bankofengland.co.uk/speech/2025/september/megan-greene-university-of-glasgow-business-school</t>
+          <t>https://www.bankofengland.co.uk/speech/2025/october/sarah-breeden-panellist-at-fintech-foundation-2025-dc-fiintech-week</t>
         </is>
       </c>
       <c r="G514" t="n">
-        <v>52933</v>
+        <v>26411</v>
       </c>
       <c r="H514" t="inlineStr">
         <is>
-          <t>bodies\BOE_2026-06-25_f943d34c.txt</t>
+          <t>bodies\BOE_2026-06-25_03ae6b31.txt</t>
         </is>
       </c>
     </row>
     <row r="515">
       <c r="A515" t="inlineStr">
         <is>
-          <t>BOE_2026-06-25_e3d44553</t>
+          <t>BOE_2026-06-25_20e40f4f</t>
         </is>
       </c>
       <c r="B515" t="inlineStr">
@@ -20992,32 +20992,32 @@
       </c>
       <c r="D515" t="inlineStr">
         <is>
-          <t>Sarah Breeden</t>
+          <t>Swati Dhingra</t>
         </is>
       </c>
       <c r="E515" t="inlineStr">
         <is>
-          <t>Building trust and supporting innovation in the multi-moneyverse − speech by Sarah Breeden</t>
+          <t>Tariffed with the same brush: confronting today’s challenges to trade − speech by Swati Dhingra</t>
         </is>
       </c>
       <c r="F515" t="inlineStr">
         <is>
-          <t>https://www.bankofengland.co.uk/speech/2025/september/sarah-breeden-keynote-speech-at-the-boe-and-warwick-business-school</t>
+          <t>https://www.bankofengland.co.uk/speech/2025/october/swati-dhingra-speech-at-the-central-bank-of-ireland-escb-cluster-2-academic-conference</t>
         </is>
       </c>
       <c r="G515" t="n">
-        <v>14233</v>
+        <v>30624</v>
       </c>
       <c r="H515" t="inlineStr">
         <is>
-          <t>bodies\BOE_2026-06-25_e3d44553.txt</t>
+          <t>bodies\BOE_2026-06-25_20e40f4f.txt</t>
         </is>
       </c>
     </row>
     <row r="516">
       <c r="A516" t="inlineStr">
         <is>
-          <t>BOE_2026-06-25_16e6b291</t>
+          <t>BOE_2026-06-25_fc72e0b8</t>
         </is>
       </c>
       <c r="B516" t="inlineStr">
@@ -21032,32 +21032,32 @@
       </c>
       <c r="D516" t="inlineStr">
         <is>
-          <t>Sarah Breeden</t>
+          <t>Huw Pill</t>
         </is>
       </c>
       <c r="E516" t="inlineStr">
         <is>
-          <t>Bumps in the road? − speech by Sarah Breeden</t>
+          <t>On QT − remarks by Huw Pill</t>
         </is>
       </c>
       <c r="F516" t="inlineStr">
         <is>
-          <t>https://www.bankofengland.co.uk/speech/2025/september/sarah-breeden-speech-cardiff-business-school-afternoon-briefing</t>
+          <t>https://www.bankofengland.co.uk/speech/2025/september/huw-pill-fireside-chat-at-the-inaugural-pictet-research-institute-symposium</t>
         </is>
       </c>
       <c r="G516" t="n">
-        <v>20886</v>
+        <v>8045</v>
       </c>
       <c r="H516" t="inlineStr">
         <is>
-          <t>bodies\BOE_2026-06-25_16e6b291.txt</t>
+          <t>bodies\BOE_2026-06-25_fc72e0b8.txt</t>
         </is>
       </c>
     </row>
     <row r="517">
       <c r="A517" t="inlineStr">
         <is>
-          <t>BOE_2026-06-25_6a9ca33c</t>
+          <t>BOE_2026-06-25_f943d34c</t>
         </is>
       </c>
       <c r="B517" t="inlineStr">
@@ -21072,32 +21072,32 @@
       </c>
       <c r="D517" t="inlineStr">
         <is>
-          <t>Alan Taylor</t>
+          <t>Megan Greene</t>
         </is>
       </c>
       <c r="E517" t="inlineStr">
         <is>
-          <t>Two-way street − speech by Alan Taylor</t>
+          <t>The supply side demands more attention − speech by Megan Greene</t>
         </is>
       </c>
       <c r="F517" t="inlineStr">
         <is>
-          <t>https://www.bankofengland.co.uk/speech/2026/april/alan-taylor-at-a-joint-conference-at-the-banque-de-france</t>
+          <t>https://www.bankofengland.co.uk/speech/2025/september/megan-greene-university-of-glasgow-business-school</t>
         </is>
       </c>
       <c r="G517" t="n">
-        <v>55037</v>
+        <v>52933</v>
       </c>
       <c r="H517" t="inlineStr">
         <is>
-          <t>bodies\BOE_2026-06-25_6a9ca33c.txt</t>
+          <t>bodies\BOE_2026-06-25_f943d34c.txt</t>
         </is>
       </c>
     </row>
     <row r="518">
       <c r="A518" t="inlineStr">
         <is>
-          <t>BOE_2026-06-25_5ab2640c</t>
+          <t>BOE_2026-06-25_e3d44553</t>
         </is>
       </c>
       <c r="B518" t="inlineStr">
@@ -21112,32 +21112,32 @@
       </c>
       <c r="D518" t="inlineStr">
         <is>
-          <t>Andrew Bailey</t>
+          <t>Sarah Breeden</t>
         </is>
       </c>
       <c r="E518" t="inlineStr">
         <is>
-          <t>Central Bank Independence – in need of further thinking - Speech by Andrew Bailey</t>
+          <t>Building trust and supporting innovation in the multi-moneyverse − speech by Sarah Breeden</t>
         </is>
       </c>
       <c r="F518" t="inlineStr">
         <is>
-          <t>https://www.bankofengland.co.uk/speech/2026/april/andrew-bailey-panellist-at-columbia-university-new-york</t>
+          <t>https://www.bankofengland.co.uk/speech/2025/september/sarah-breeden-keynote-speech-at-the-boe-and-warwick-business-school</t>
         </is>
       </c>
       <c r="G518" t="n">
-        <v>27433</v>
+        <v>14233</v>
       </c>
       <c r="H518" t="inlineStr">
         <is>
-          <t>bodies\BOE_2026-06-25_5ab2640c.txt</t>
+          <t>bodies\BOE_2026-06-25_e3d44553.txt</t>
         </is>
       </c>
     </row>
     <row r="519">
       <c r="A519" t="inlineStr">
         <is>
-          <t>BOE_2026-06-25_9188f4a4</t>
+          <t>BOE_2026-06-25_16e6b291</t>
         </is>
       </c>
       <c r="B519" t="inlineStr">
@@ -21152,32 +21152,32 @@
       </c>
       <c r="D519" t="inlineStr">
         <is>
-          <t>David Bailey</t>
+          <t>Sarah Breeden</t>
         </is>
       </c>
       <c r="E519" t="inlineStr">
         <is>
-          <t>Building a banking regime for the future - speech by David Bailey</t>
+          <t>Bumps in the road? − speech by Sarah Breeden</t>
         </is>
       </c>
       <c r="F519" t="inlineStr">
         <is>
-          <t>https://www.bankofengland.co.uk/speech/2026/april/david-bailey-speech-jp-morgan-uk-banks-asset-and-liability-mgmt-conference</t>
+          <t>https://www.bankofengland.co.uk/speech/2025/september/sarah-breeden-speech-cardiff-business-school-afternoon-briefing</t>
         </is>
       </c>
       <c r="G519" t="n">
-        <v>26715</v>
+        <v>20886</v>
       </c>
       <c r="H519" t="inlineStr">
         <is>
-          <t>bodies\BOE_2026-06-25_9188f4a4.txt</t>
+          <t>bodies\BOE_2026-06-25_16e6b291.txt</t>
         </is>
       </c>
     </row>
     <row r="520">
       <c r="A520" t="inlineStr">
         <is>
-          <t>BOE_2026-06-25_faebfad9</t>
+          <t>BOE_2026-06-25_6a9ca33c</t>
         </is>
       </c>
       <c r="B520" t="inlineStr">
@@ -21192,32 +21192,32 @@
       </c>
       <c r="D520" t="inlineStr">
         <is>
-          <t>Sarah Breeden</t>
+          <t>Alan Taylor</t>
         </is>
       </c>
       <c r="E520" t="inlineStr">
         <is>
-          <t>This time is different? Speech by Sarah Breeden</t>
+          <t>Two-way street − speech by Alan Taylor</t>
         </is>
       </c>
       <c r="F520" t="inlineStr">
         <is>
-          <t>https://www.bankofengland.co.uk/speech/2026/april/sarah-breeden-at-the-program-on-international-financial-systems-and-harvard-law-school</t>
+          <t>https://www.bankofengland.co.uk/speech/2026/april/alan-taylor-at-a-joint-conference-at-the-banque-de-france</t>
         </is>
       </c>
       <c r="G520" t="n">
-        <v>21324</v>
+        <v>55037</v>
       </c>
       <c r="H520" t="inlineStr">
         <is>
-          <t>bodies\BOE_2026-06-25_faebfad9.txt</t>
+          <t>bodies\BOE_2026-06-25_6a9ca33c.txt</t>
         </is>
       </c>
     </row>
     <row r="521">
       <c r="A521" t="inlineStr">
         <is>
-          <t>BOE_2026-06-25_6224393e</t>
+          <t>BOE_2026-06-25_5ab2640c</t>
         </is>
       </c>
       <c r="B521" t="inlineStr">
@@ -21237,27 +21237,27 @@
       </c>
       <c r="E521" t="inlineStr">
         <is>
-          <t>The world today – remarks by Andrew Bailey</t>
+          <t>Central Bank Independence – in need of further thinking - Speech by Andrew Bailey</t>
         </is>
       </c>
       <c r="F521" t="inlineStr">
         <is>
-          <t>https://www.bankofengland.co.uk/speech/2026/february/andrew-bailey-speech-at-the-imf-saudi-ministry-of-finance</t>
+          <t>https://www.bankofengland.co.uk/speech/2026/april/andrew-bailey-panellist-at-columbia-university-new-york</t>
         </is>
       </c>
       <c r="G521" t="n">
-        <v>13796</v>
+        <v>27433</v>
       </c>
       <c r="H521" t="inlineStr">
         <is>
-          <t>bodies\BOE_2026-06-25_6224393e.txt</t>
+          <t>bodies\BOE_2026-06-25_5ab2640c.txt</t>
         </is>
       </c>
     </row>
     <row r="522">
       <c r="A522" t="inlineStr">
         <is>
-          <t>BOE_2026-06-25_cb97019c</t>
+          <t>BOE_2026-06-25_9188f4a4</t>
         </is>
       </c>
       <c r="B522" t="inlineStr">
@@ -21272,32 +21272,32 @@
       </c>
       <c r="D522" t="inlineStr">
         <is>
-          <t>Sarah Breeden</t>
+          <t>David Bailey</t>
         </is>
       </c>
       <c r="E522" t="inlineStr">
         <is>
-          <t>Talking ’bout next generation − speech by Sarah Breeden</t>
+          <t>Building a banking regime for the future - speech by David Bailey</t>
         </is>
       </c>
       <c r="F522" t="inlineStr">
         <is>
-          <t>https://www.bankofengland.co.uk/speech/2026/february/sarah-breeden-keynote-speech-at-the-city-financial-annual-payments-regulation-and-innovation-summit</t>
+          <t>https://www.bankofengland.co.uk/speech/2026/april/david-bailey-speech-jp-morgan-uk-banks-asset-and-liability-mgmt-conference</t>
         </is>
       </c>
       <c r="G522" t="n">
-        <v>25726</v>
+        <v>26715</v>
       </c>
       <c r="H522" t="inlineStr">
         <is>
-          <t>bodies\BOE_2026-06-25_cb97019c.txt</t>
+          <t>bodies\BOE_2026-06-25_9188f4a4.txt</t>
         </is>
       </c>
     </row>
     <row r="523">
       <c r="A523" t="inlineStr">
         <is>
-          <t>BOE_2026-06-25_64dc78ad</t>
+          <t>BOE_2026-06-25_faebfad9</t>
         </is>
       </c>
       <c r="B523" t="inlineStr">
@@ -21310,30 +21310,34 @@
           <t>BOE</t>
         </is>
       </c>
-      <c r="D523" t="inlineStr"/>
+      <c r="D523" t="inlineStr">
+        <is>
+          <t>Sarah Breeden</t>
+        </is>
+      </c>
       <c r="E523" t="inlineStr">
         <is>
-          <t>Slides from Huw Pill’s fireside chat at Santander UK’s macroeconomic event</t>
+          <t>This time is different? Speech by Sarah Breeden</t>
         </is>
       </c>
       <c r="F523" t="inlineStr">
         <is>
-          <t>https://www.bankofengland.co.uk/speech/2026/february/slides-from-huw-pill-fireside-chat-at-santander-event</t>
+          <t>https://www.bankofengland.co.uk/speech/2026/april/sarah-breeden-at-the-program-on-international-financial-systems-and-harvard-law-school</t>
         </is>
       </c>
       <c r="G523" t="n">
-        <v>1828</v>
+        <v>21324</v>
       </c>
       <c r="H523" t="inlineStr">
         <is>
-          <t>bodies\BOE_2026-06-25_64dc78ad.txt</t>
+          <t>bodies\BOE_2026-06-25_faebfad9.txt</t>
         </is>
       </c>
     </row>
     <row r="524">
       <c r="A524" t="inlineStr">
         <is>
-          <t>BOE_2026-06-25_78fb7fe0</t>
+          <t>BOE_2026-06-25_6224393e</t>
         </is>
       </c>
       <c r="B524" t="inlineStr">
@@ -21348,32 +21352,32 @@
       </c>
       <c r="D524" t="inlineStr">
         <is>
-          <t>Alan Taylor</t>
+          <t>Andrew Bailey</t>
         </is>
       </c>
       <c r="E524" t="inlineStr">
         <is>
-          <t>Driving over the peak, or a false summit? − speech by Alan Taylor</t>
+          <t>The world today – remarks by Andrew Bailey</t>
         </is>
       </c>
       <c r="F524" t="inlineStr">
         <is>
-          <t>https://www.bankofengland.co.uk/speech/2026/january/alan-taylor-speech-at-the-national-university-of-singapore</t>
+          <t>https://www.bankofengland.co.uk/speech/2026/february/andrew-bailey-speech-at-the-imf-saudi-ministry-of-finance</t>
         </is>
       </c>
       <c r="G524" t="n">
-        <v>55010</v>
+        <v>13796</v>
       </c>
       <c r="H524" t="inlineStr">
         <is>
-          <t>bodies\BOE_2026-06-25_78fb7fe0.txt</t>
+          <t>bodies\BOE_2026-06-25_6224393e.txt</t>
         </is>
       </c>
     </row>
     <row r="525">
       <c r="A525" t="inlineStr">
         <is>
-          <t>BOE_2026-06-25_628efeb3</t>
+          <t>BOE_2026-06-25_cb97019c</t>
         </is>
       </c>
       <c r="B525" t="inlineStr">
@@ -21388,32 +21392,32 @@
       </c>
       <c r="D525" t="inlineStr">
         <is>
-          <t>Andrew Bailey</t>
+          <t>Sarah Breeden</t>
         </is>
       </c>
       <c r="E525" t="inlineStr">
         <is>
-          <t>Global imbalances in a more fragmented world – remarks by Andrew Bailey</t>
+          <t>Talking ’bout next generation − speech by Sarah Breeden</t>
         </is>
       </c>
       <c r="F525" t="inlineStr">
         <is>
-          <t>https://www.bankofengland.co.uk/speech/2026/january/andrew-bailey-meeting-of-the-bellagio-group-2026-at-the-boe</t>
+          <t>https://www.bankofengland.co.uk/speech/2026/february/sarah-breeden-keynote-speech-at-the-city-financial-annual-payments-regulation-and-innovation-summit</t>
         </is>
       </c>
       <c r="G525" t="n">
-        <v>12168</v>
+        <v>25726</v>
       </c>
       <c r="H525" t="inlineStr">
         <is>
-          <t>bodies\BOE_2026-06-25_628efeb3.txt</t>
+          <t>bodies\BOE_2026-06-25_cb97019c.txt</t>
         </is>
       </c>
     </row>
     <row r="526">
       <c r="A526" t="inlineStr">
         <is>
-          <t>BOE_2026-06-25_b9e45e71</t>
+          <t>BOE_2026-06-25_64dc78ad</t>
         </is>
       </c>
       <c r="B526" t="inlineStr">
@@ -21426,34 +21430,30 @@
           <t>BOE</t>
         </is>
       </c>
-      <c r="D526" t="inlineStr">
-        <is>
-          <t>Dave Ramsden</t>
-        </is>
-      </c>
+      <c r="D526" t="inlineStr"/>
       <c r="E526" t="inlineStr">
         <is>
-          <t>The evolution of the Bank’s approach to resolution − speech by Dave Ramsden</t>
+          <t>Slides from Huw Pill’s fireside chat at Santander UK’s macroeconomic event</t>
         </is>
       </c>
       <c r="F526" t="inlineStr">
         <is>
-          <t>https://www.bankofengland.co.uk/speech/2026/january/dave-ramsden-speech-at-kings-college-london-the-evolution-of-resolution</t>
+          <t>https://www.bankofengland.co.uk/speech/2026/february/slides-from-huw-pill-fireside-chat-at-santander-event</t>
         </is>
       </c>
       <c r="G526" t="n">
-        <v>33066</v>
+        <v>1828</v>
       </c>
       <c r="H526" t="inlineStr">
         <is>
-          <t>bodies\BOE_2026-06-25_b9e45e71.txt</t>
+          <t>bodies\BOE_2026-06-25_64dc78ad.txt</t>
         </is>
       </c>
     </row>
     <row r="527">
       <c r="A527" t="inlineStr">
         <is>
-          <t>BOE_2026-06-25_4e3d7aef</t>
+          <t>BOE_2026-06-25_78fb7fe0</t>
         </is>
       </c>
       <c r="B527" t="inlineStr">
@@ -21468,37 +21468,37 @@
       </c>
       <c r="D527" t="inlineStr">
         <is>
-          <t>Megan Greene</t>
+          <t>Alan Taylor</t>
         </is>
       </c>
       <c r="E527" t="inlineStr">
         <is>
-          <t>Forks in the Curve: whether and how to respond to monetary policy divergence - speech by Megan Greene</t>
+          <t>Driving over the peak, or a false summit? − speech by Alan Taylor</t>
         </is>
       </c>
       <c r="F527" t="inlineStr">
         <is>
-          <t>https://www.bankofengland.co.uk/speech/2026/january/megan-greene-speech-at-the-resolution-foundation-worlds-apart</t>
+          <t>https://www.bankofengland.co.uk/speech/2026/january/alan-taylor-speech-at-the-national-university-of-singapore</t>
         </is>
       </c>
       <c r="G527" t="n">
-        <v>51513</v>
+        <v>55010</v>
       </c>
       <c r="H527" t="inlineStr">
         <is>
-          <t>bodies\BOE_2026-06-25_4e3d7aef.txt</t>
+          <t>bodies\BOE_2026-06-25_78fb7fe0.txt</t>
         </is>
       </c>
     </row>
     <row r="528">
       <c r="A528" t="inlineStr">
         <is>
-          <t>BOE_2026-07-21_b0bf9593</t>
+          <t>BOE_2026-06-25_628efeb3</t>
         </is>
       </c>
       <c r="B528" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="C528" t="inlineStr">
@@ -21508,32 +21508,32 @@
       </c>
       <c r="D528" t="inlineStr">
         <is>
-          <t>Catherine L. Mann</t>
+          <t>Andrew Bailey</t>
         </is>
       </c>
       <c r="E528" t="inlineStr">
         <is>
-          <t>Mixed signals, research findings, and policy judgements − speech by Catherine L. Mann</t>
+          <t>Global imbalances in a more fragmented world – remarks by Andrew Bailey</t>
         </is>
       </c>
       <c r="F528" t="inlineStr">
         <is>
-          <t>https://www.bankofengland.co.uk/speech/2026/july/catherine-l-mann-fireside-chat-at-the-natixis-cib-conference-on-private-debt</t>
+          <t>https://www.bankofengland.co.uk/speech/2026/january/andrew-bailey-meeting-of-the-bellagio-group-2026-at-the-boe</t>
         </is>
       </c>
       <c r="G528" t="n">
-        <v>33789</v>
+        <v>12168</v>
       </c>
       <c r="H528" t="inlineStr">
         <is>
-          <t>bodies\BOE_2026-07-21_b0bf9593.txt</t>
+          <t>bodies\BOE_2026-06-25_628efeb3.txt</t>
         </is>
       </c>
     </row>
     <row r="529">
       <c r="A529" t="inlineStr">
         <is>
-          <t>BOE_2026-06-25_5d89c9a7</t>
+          <t>BOE_2026-06-25_b9e45e71</t>
         </is>
       </c>
       <c r="B529" t="inlineStr">
@@ -21548,32 +21548,32 @@
       </c>
       <c r="D529" t="inlineStr">
         <is>
-          <t>Alan Taylor</t>
+          <t>Dave Ramsden</t>
         </is>
       </c>
       <c r="E529" t="inlineStr">
         <is>
-          <t>Central reservations − speech by Alan Taylor</t>
+          <t>The evolution of the Bank’s approach to resolution − speech by Dave Ramsden</t>
         </is>
       </c>
       <c r="F529" t="inlineStr">
         <is>
-          <t>https://www.bankofengland.co.uk/speech/2026/june/alan-taylor-speech-at-the-barclays-and-centre-for-economic-policy-research</t>
+          <t>https://www.bankofengland.co.uk/speech/2026/january/dave-ramsden-speech-at-kings-college-london-the-evolution-of-resolution</t>
         </is>
       </c>
       <c r="G529" t="n">
-        <v>50881</v>
+        <v>33066</v>
       </c>
       <c r="H529" t="inlineStr">
         <is>
-          <t>bodies\BOE_2026-06-25_5d89c9a7.txt</t>
+          <t>bodies\BOE_2026-06-25_b9e45e71.txt</t>
         </is>
       </c>
     </row>
     <row r="530">
       <c r="A530" t="inlineStr">
         <is>
-          <t>BOE_2026-06-25_18d2378b</t>
+          <t>BOE_2026-06-25_4e3d7aef</t>
         </is>
       </c>
       <c r="B530" t="inlineStr">
@@ -21593,27 +21593,27 @@
       </c>
       <c r="E530" t="inlineStr">
         <is>
-          <t>Here we go again? Assessing the inflation risks of the recent energy shock − speech by Megan Greene</t>
+          <t>Forks in the Curve: whether and how to respond to monetary policy divergence - speech by Megan Greene</t>
         </is>
       </c>
       <c r="F530" t="inlineStr">
         <is>
-          <t>https://www.bankofengland.co.uk/speech/2026/june/megan-greene-speech-at-university-of-derby-business-school</t>
+          <t>https://www.bankofengland.co.uk/speech/2026/january/megan-greene-speech-at-the-resolution-foundation-worlds-apart</t>
         </is>
       </c>
       <c r="G530" t="n">
-        <v>627</v>
+        <v>51513</v>
       </c>
       <c r="H530" t="inlineStr">
         <is>
-          <t>bodies\BOE_2026-06-25_18d2378b.txt</t>
+          <t>bodies\BOE_2026-06-25_4e3d7aef.txt</t>
         </is>
       </c>
     </row>
     <row r="531">
       <c r="A531" t="inlineStr">
         <is>
-          <t>BOE_2026-07-21_e2a07525</t>
+          <t>BOE_2026-07-21_b0bf9593</t>
         </is>
       </c>
       <c r="B531" t="inlineStr">
@@ -21628,32 +21628,32 @@
       </c>
       <c r="D531" t="inlineStr">
         <is>
-          <t>Sarah Breeden</t>
+          <t>Catherine L. Mann</t>
         </is>
       </c>
       <c r="E531" t="inlineStr">
         <is>
-          <t>Agents of change − speech by Sarah Breeden</t>
+          <t>Mixed signals, research findings, and policy judgements − speech by Catherine L. Mann</t>
         </is>
       </c>
       <c r="F531" t="inlineStr">
         <is>
-          <t>https://www.bankofengland.co.uk/speech/2026/june/sarah-breeden-panel-at-the-european-central-bank-forum-on-central-banking-2026</t>
+          <t>https://www.bankofengland.co.uk/speech/2026/july/catherine-l-mann-fireside-chat-at-the-natixis-cib-conference-on-private-debt</t>
         </is>
       </c>
       <c r="G531" t="n">
-        <v>19404</v>
+        <v>33789</v>
       </c>
       <c r="H531" t="inlineStr">
         <is>
-          <t>bodies\BOE_2026-07-21_e2a07525.txt</t>
+          <t>bodies\BOE_2026-07-21_b0bf9593.txt</t>
         </is>
       </c>
     </row>
     <row r="532">
       <c r="A532" t="inlineStr">
         <is>
-          <t>BOE_2026-06-25_9858f896</t>
+          <t>BOE_2026-06-25_5d89c9a7</t>
         </is>
       </c>
       <c r="B532" t="inlineStr">
@@ -21673,27 +21673,27 @@
       </c>
       <c r="E532" t="inlineStr">
         <is>
-          <t>Stopping for gas − speech by Alan Taylor</t>
+          <t>Central reservations − speech by Alan Taylor</t>
         </is>
       </c>
       <c r="F532" t="inlineStr">
         <is>
-          <t>https://www.bankofengland.co.uk/speech/2026/march/alan-taylor-exante-datas-10-year-anniversary-macro-conference</t>
+          <t>https://www.bankofengland.co.uk/speech/2026/june/alan-taylor-speech-at-the-barclays-and-centre-for-economic-policy-research</t>
         </is>
       </c>
       <c r="G532" t="n">
-        <v>59353</v>
+        <v>50881</v>
       </c>
       <c r="H532" t="inlineStr">
         <is>
-          <t>bodies\BOE_2026-06-25_9858f896.txt</t>
+          <t>bodies\BOE_2026-06-25_5d89c9a7.txt</t>
         </is>
       </c>
     </row>
     <row r="533">
       <c r="A533" t="inlineStr">
         <is>
-          <t>BOE_2026-06-25_71c27795</t>
+          <t>BOE_2026-06-25_18d2378b</t>
         </is>
       </c>
       <c r="B533" t="inlineStr">
@@ -21708,37 +21708,37 @@
       </c>
       <c r="D533" t="inlineStr">
         <is>
-          <t>Huw Pill</t>
+          <t>Megan Greene</t>
         </is>
       </c>
       <c r="E533" t="inlineStr">
         <is>
-          <t>Robustness - speech by Huw Pill</t>
+          <t>Here we go again? Assessing the inflation risks of the recent energy shock − speech by Megan Greene</t>
         </is>
       </c>
       <c r="F533" t="inlineStr">
         <is>
-          <t>https://www.bankofengland.co.uk/speech/2026/march/huw-pill-speech-at-national-bank-of-the-republic-of-north-macedonia-and-suerf-conference</t>
+          <t>https://www.bankofengland.co.uk/speech/2026/june/megan-greene-speech-at-university-of-derby-business-school</t>
         </is>
       </c>
       <c r="G533" t="n">
-        <v>738</v>
+        <v>627</v>
       </c>
       <c r="H533" t="inlineStr">
         <is>
-          <t>bodies\BOE_2026-06-25_71c27795.txt</t>
+          <t>bodies\BOE_2026-06-25_18d2378b.txt</t>
         </is>
       </c>
     </row>
     <row r="534">
       <c r="A534" t="inlineStr">
         <is>
-          <t>BOE_2026-06-25_de15e418</t>
+          <t>BOE_2026-07-21_e2a07525</t>
         </is>
       </c>
       <c r="B534" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="C534" t="inlineStr">
@@ -21748,32 +21748,32 @@
       </c>
       <c r="D534" t="inlineStr">
         <is>
-          <t>Alan Taylor</t>
+          <t>Sarah Breeden</t>
         </is>
       </c>
       <c r="E534" t="inlineStr">
         <is>
-          <t>Getting the right directions − speech by Alan Taylor</t>
+          <t>Agents of change − speech by Sarah Breeden</t>
         </is>
       </c>
       <c r="F534" t="inlineStr">
         <is>
-          <t>https://www.bankofengland.co.uk/speech/2026/march/speech-by-alan-taylor-getting-the-right-directions</t>
+          <t>https://www.bankofengland.co.uk/speech/2026/june/sarah-breeden-panel-at-the-european-central-bank-forum-on-central-banking-2026</t>
         </is>
       </c>
       <c r="G534" t="n">
-        <v>33447</v>
+        <v>19404</v>
       </c>
       <c r="H534" t="inlineStr">
         <is>
-          <t>bodies\BOE_2026-06-25_de15e418.txt</t>
+          <t>bodies\BOE_2026-07-21_e2a07525.txt</t>
         </is>
       </c>
     </row>
     <row r="535">
       <c r="A535" t="inlineStr">
         <is>
-          <t>BOE_2026-06-25_6f85c893</t>
+          <t>BOE_2026-06-25_9858f896</t>
         </is>
       </c>
       <c r="B535" t="inlineStr">
@@ -21788,32 +21788,32 @@
       </c>
       <c r="D535" t="inlineStr">
         <is>
-          <t>Andrew Bailey</t>
+          <t>Alan Taylor</t>
         </is>
       </c>
       <c r="E535" t="inlineStr">
         <is>
-          <t>Can AI make cutlery? -  speech by Andrew Bailey</t>
+          <t>Stopping for gas − speech by Alan Taylor</t>
         </is>
       </c>
       <c r="F535" t="inlineStr">
         <is>
-          <t>https://www.bankofengland.co.uk/speech/2026/may/andrew-bailey-speech-at-cutlers-feast-sheffield</t>
+          <t>https://www.bankofengland.co.uk/speech/2026/march/alan-taylor-exante-datas-10-year-anniversary-macro-conference</t>
         </is>
       </c>
       <c r="G535" t="n">
-        <v>25929</v>
+        <v>59353</v>
       </c>
       <c r="H535" t="inlineStr">
         <is>
-          <t>bodies\BOE_2026-06-25_6f85c893.txt</t>
+          <t>bodies\BOE_2026-06-25_9858f896.txt</t>
         </is>
       </c>
     </row>
     <row r="536">
       <c r="A536" t="inlineStr">
         <is>
-          <t>BOE_2026-06-25_602fcf5a</t>
+          <t>BOE_2026-06-25_71c27795</t>
         </is>
       </c>
       <c r="B536" t="inlineStr">
@@ -21828,32 +21828,32 @@
       </c>
       <c r="D536" t="inlineStr">
         <is>
-          <t>Andrew Bailey</t>
+          <t>Huw Pill</t>
         </is>
       </c>
       <c r="E536" t="inlineStr">
         <is>
-          <t>Remaining anchored: Monetary Policy in an unpredictable world - speech by Andrew Bailey</t>
+          <t>Robustness - speech by Huw Pill</t>
         </is>
       </c>
       <c r="F536" t="inlineStr">
         <is>
-          <t>https://www.bankofengland.co.uk/speech/2026/may/andrew-bailey-speech-at-the-reykjavik-2026-economic-conference</t>
+          <t>https://www.bankofengland.co.uk/speech/2026/march/huw-pill-speech-at-national-bank-of-the-republic-of-north-macedonia-and-suerf-conference</t>
         </is>
       </c>
       <c r="G536" t="n">
-        <v>17796</v>
+        <v>738</v>
       </c>
       <c r="H536" t="inlineStr">
         <is>
-          <t>bodies\BOE_2026-06-25_602fcf5a.txt</t>
+          <t>bodies\BOE_2026-06-25_71c27795.txt</t>
         </is>
       </c>
     </row>
     <row r="537">
       <c r="A537" t="inlineStr">
         <is>
-          <t>BOE_2026-06-25_44a80d6f</t>
+          <t>BOE_2026-06-25_de15e418</t>
         </is>
       </c>
       <c r="B537" t="inlineStr">
@@ -21868,63 +21868,183 @@
       </c>
       <c r="D537" t="inlineStr">
         <is>
-          <t>Catherine L. Mann</t>
+          <t>Alan Taylor</t>
         </is>
       </c>
       <c r="E537" t="inlineStr">
         <is>
-          <t>Old exposures, new actors: implications for monetary policy of the UK’s external imbalances − speech by Catherine L. Mann</t>
+          <t>Getting the right directions − speech by Alan Taylor</t>
         </is>
       </c>
       <c r="F537" t="inlineStr">
         <is>
-          <t>https://www.bankofengland.co.uk/speech/2026/may/catherine-l-mann-speech-at-the-london-school-of-economics</t>
+          <t>https://www.bankofengland.co.uk/speech/2026/march/speech-by-alan-taylor-getting-the-right-directions</t>
         </is>
       </c>
       <c r="G537" t="n">
-        <v>56210</v>
+        <v>33447</v>
       </c>
       <c r="H537" t="inlineStr">
         <is>
-          <t>bodies\BOE_2026-06-25_44a80d6f.txt</t>
+          <t>bodies\BOE_2026-06-25_de15e418.txt</t>
         </is>
       </c>
     </row>
     <row r="538">
       <c r="A538" t="inlineStr">
         <is>
+          <t>BOE_2026-06-25_6f85c893</t>
+        </is>
+      </c>
+      <c r="B538" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="C538" t="inlineStr">
+        <is>
+          <t>BOE</t>
+        </is>
+      </c>
+      <c r="D538" t="inlineStr">
+        <is>
+          <t>Andrew Bailey</t>
+        </is>
+      </c>
+      <c r="E538" t="inlineStr">
+        <is>
+          <t>Can AI make cutlery? -  speech by Andrew Bailey</t>
+        </is>
+      </c>
+      <c r="F538" t="inlineStr">
+        <is>
+          <t>https://www.bankofengland.co.uk/speech/2026/may/andrew-bailey-speech-at-cutlers-feast-sheffield</t>
+        </is>
+      </c>
+      <c r="G538" t="n">
+        <v>25929</v>
+      </c>
+      <c r="H538" t="inlineStr">
+        <is>
+          <t>bodies\BOE_2026-06-25_6f85c893.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="539">
+      <c r="A539" t="inlineStr">
+        <is>
+          <t>BOE_2026-06-25_602fcf5a</t>
+        </is>
+      </c>
+      <c r="B539" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="C539" t="inlineStr">
+        <is>
+          <t>BOE</t>
+        </is>
+      </c>
+      <c r="D539" t="inlineStr">
+        <is>
+          <t>Andrew Bailey</t>
+        </is>
+      </c>
+      <c r="E539" t="inlineStr">
+        <is>
+          <t>Remaining anchored: Monetary Policy in an unpredictable world - speech by Andrew Bailey</t>
+        </is>
+      </c>
+      <c r="F539" t="inlineStr">
+        <is>
+          <t>https://www.bankofengland.co.uk/speech/2026/may/andrew-bailey-speech-at-the-reykjavik-2026-economic-conference</t>
+        </is>
+      </c>
+      <c r="G539" t="n">
+        <v>17796</v>
+      </c>
+      <c r="H539" t="inlineStr">
+        <is>
+          <t>bodies\BOE_2026-06-25_602fcf5a.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="540">
+      <c r="A540" t="inlineStr">
+        <is>
+          <t>BOE_2026-06-25_44a80d6f</t>
+        </is>
+      </c>
+      <c r="B540" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="C540" t="inlineStr">
+        <is>
+          <t>BOE</t>
+        </is>
+      </c>
+      <c r="D540" t="inlineStr">
+        <is>
+          <t>Catherine L. Mann</t>
+        </is>
+      </c>
+      <c r="E540" t="inlineStr">
+        <is>
+          <t>Old exposures, new actors: implications for monetary policy of the UK’s external imbalances − speech by Catherine L. Mann</t>
+        </is>
+      </c>
+      <c r="F540" t="inlineStr">
+        <is>
+          <t>https://www.bankofengland.co.uk/speech/2026/may/catherine-l-mann-speech-at-the-london-school-of-economics</t>
+        </is>
+      </c>
+      <c r="G540" t="n">
+        <v>56210</v>
+      </c>
+      <c r="H540" t="inlineStr">
+        <is>
+          <t>bodies\BOE_2026-06-25_44a80d6f.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="541">
+      <c r="A541" t="inlineStr">
+        <is>
           <t>BOE_2026-06-25_9a26b05a</t>
         </is>
       </c>
-      <c r="B538" t="inlineStr">
+      <c r="B541" t="inlineStr">
         <is>
           <t>2026-06-25</t>
         </is>
       </c>
-      <c r="C538" t="inlineStr">
+      <c r="C541" t="inlineStr">
         <is>
           <t>BOE</t>
         </is>
       </c>
-      <c r="D538" t="inlineStr">
+      <c r="D541" t="inlineStr">
         <is>
           <t>Sarah Breeden</t>
         </is>
       </c>
-      <c r="E538" t="inlineStr">
+      <c r="E541" t="inlineStr">
         <is>
           <t>Modernising money and markets − speech by Sarah Breeden</t>
         </is>
       </c>
-      <c r="F538" t="inlineStr">
+      <c r="F541" t="inlineStr">
         <is>
           <t>https://www.bankofengland.co.uk/speech/2026/may/sarah-breeden-speech-at-city-week-the-future-of-money-in-a-digital-world</t>
         </is>
       </c>
-      <c r="G538" t="n">
+      <c r="G541" t="n">
         <v>28703</v>
       </c>
-      <c r="H538" t="inlineStr">
+      <c r="H541" t="inlineStr">
         <is>
           <t>bodies\BOE_2026-06-25_9a26b05a.txt</t>
         </is>
